--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ177"/>
+  <dimension ref="A1:AZ178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20592,6 +20592,118 @@
       <c r="AZ177" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129124091</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>137209425</v>
+      </c>
+      <c r="B178" t="n">
+        <v>79511</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Blåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>421202</v>
+      </c>
+      <c r="R178" t="n">
+        <v>6788653</v>
+      </c>
+      <c r="S178" t="n">
+        <v>9</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137209425</t>
         </is>
       </c>
     </row>
@@ -20773,6 +20885,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ178"/>
+  <dimension ref="A1:AZ179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8548,32 +8548,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129124187</v>
+        <v>137237604</v>
       </c>
       <c r="B72" t="n">
-        <v>78730</v>
+        <v>79501</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8583,13 +8583,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>421639</v>
+        <v>421176</v>
       </c>
       <c r="R72" t="n">
-        <v>6788393</v>
+        <v>6788647</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8613,22 +8613,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8643,27 +8643,27 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124187</t>
+          <t>https://artportalen.se/Sighting/137237604</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129095733</v>
+        <v>129124187</v>
       </c>
       <c r="B73" t="n">
-        <v>79084</v>
+        <v>78730</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8671,34 +8671,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>421655</v>
+        <v>421639</v>
       </c>
       <c r="R73" t="n">
-        <v>6787687</v>
+        <v>6788393</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8755,24 +8755,24 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095733</t>
+          <t>https://artportalen.se/Sighting/129124187</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129124137</v>
+        <v>129095733</v>
       </c>
       <c r="B74" t="n">
         <v>79084</v>
@@ -8803,14 +8803,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>421312</v>
+        <v>421655</v>
       </c>
       <c r="R74" t="n">
-        <v>6788393</v>
+        <v>6787687</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8867,24 +8867,24 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124137</t>
+          <t>https://artportalen.se/Sighting/129095733</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129124138</v>
+        <v>129124137</v>
       </c>
       <c r="B75" t="n">
         <v>79084</v>
@@ -8919,10 +8919,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>421292</v>
+        <v>421312</v>
       </c>
       <c r="R75" t="n">
-        <v>6788456</v>
+        <v>6788393</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8990,13 +8990,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124138</t>
+          <t>https://artportalen.se/Sighting/129124137</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129124139</v>
+        <v>129124138</v>
       </c>
       <c r="B76" t="n">
         <v>79084</v>
@@ -9031,10 +9031,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>421354</v>
+        <v>421292</v>
       </c>
       <c r="R76" t="n">
-        <v>6788463</v>
+        <v>6788456</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9102,13 +9102,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124139</t>
+          <t>https://artportalen.se/Sighting/129124138</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129124140</v>
+        <v>129124139</v>
       </c>
       <c r="B77" t="n">
         <v>79084</v>
@@ -9143,10 +9143,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>421656</v>
+        <v>421354</v>
       </c>
       <c r="R77" t="n">
-        <v>6787791</v>
+        <v>6788463</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9214,13 +9214,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124140</t>
+          <t>https://artportalen.se/Sighting/129124139</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129124141</v>
+        <v>129124140</v>
       </c>
       <c r="B78" t="n">
         <v>79084</v>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>421616</v>
+        <v>421656</v>
       </c>
       <c r="R78" t="n">
-        <v>6787883</v>
+        <v>6787791</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9326,13 +9326,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124141</t>
+          <t>https://artportalen.se/Sighting/129124140</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129124142</v>
+        <v>129124141</v>
       </c>
       <c r="B79" t="n">
         <v>79084</v>
@@ -9367,10 +9367,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>421594</v>
+        <v>421616</v>
       </c>
       <c r="R79" t="n">
-        <v>6787870</v>
+        <v>6787883</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9438,13 +9438,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124142</t>
+          <t>https://artportalen.se/Sighting/129124141</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129124143</v>
+        <v>129124142</v>
       </c>
       <c r="B80" t="n">
         <v>79084</v>
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>421596</v>
+        <v>421594</v>
       </c>
       <c r="R80" t="n">
-        <v>6787835</v>
+        <v>6787870</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9550,13 +9550,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124143</t>
+          <t>https://artportalen.se/Sighting/129124142</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129124144</v>
+        <v>129124143</v>
       </c>
       <c r="B81" t="n">
         <v>79084</v>
@@ -9591,10 +9591,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>421602</v>
+        <v>421596</v>
       </c>
       <c r="R81" t="n">
-        <v>6787829</v>
+        <v>6787835</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9626,7 +9626,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9662,13 +9662,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124144</t>
+          <t>https://artportalen.se/Sighting/129124143</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129124145</v>
+        <v>129124144</v>
       </c>
       <c r="B82" t="n">
         <v>79084</v>
@@ -9703,10 +9703,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>421591</v>
+        <v>421602</v>
       </c>
       <c r="R82" t="n">
-        <v>6787819</v>
+        <v>6787829</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9774,16 +9774,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124145</t>
+          <t>https://artportalen.se/Sighting/129124144</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129093027</v>
+        <v>129124145</v>
       </c>
       <c r="B83" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9791,34 +9791,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>421341</v>
+        <v>421591</v>
       </c>
       <c r="R83" t="n">
-        <v>6788261</v>
+        <v>6787819</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9875,24 +9875,24 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093027</t>
+          <t>https://artportalen.se/Sighting/129124145</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129093086</v>
+        <v>129093027</v>
       </c>
       <c r="B84" t="n">
         <v>79946</v>
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>421380</v>
+        <v>421341</v>
       </c>
       <c r="R84" t="n">
-        <v>6788287</v>
+        <v>6788261</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9998,13 +9998,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093086</t>
+          <t>https://artportalen.se/Sighting/129093027</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129093766</v>
+        <v>129093086</v>
       </c>
       <c r="B85" t="n">
         <v>79946</v>
@@ -10039,10 +10039,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>421371</v>
+        <v>421380</v>
       </c>
       <c r="R85" t="n">
-        <v>6788472</v>
+        <v>6788287</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10110,13 +10110,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093766</t>
+          <t>https://artportalen.se/Sighting/129093086</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129094072</v>
+        <v>129093766</v>
       </c>
       <c r="B86" t="n">
         <v>79946</v>
@@ -10151,10 +10151,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>421379</v>
+        <v>421371</v>
       </c>
       <c r="R86" t="n">
-        <v>6788540</v>
+        <v>6788472</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10222,13 +10222,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094072</t>
+          <t>https://artportalen.se/Sighting/129093766</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129094551</v>
+        <v>129094072</v>
       </c>
       <c r="B87" t="n">
         <v>79946</v>
@@ -10263,10 +10263,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>421564</v>
+        <v>421379</v>
       </c>
       <c r="R87" t="n">
-        <v>6788544</v>
+        <v>6788540</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10334,13 +10334,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094551</t>
+          <t>https://artportalen.se/Sighting/129094072</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129095002</v>
+        <v>129094551</v>
       </c>
       <c r="B88" t="n">
         <v>79946</v>
@@ -10375,10 +10375,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>421507</v>
+        <v>421564</v>
       </c>
       <c r="R88" t="n">
-        <v>6788435</v>
+        <v>6788544</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10446,13 +10446,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095002</t>
+          <t>https://artportalen.se/Sighting/129094551</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129095786</v>
+        <v>129095002</v>
       </c>
       <c r="B89" t="n">
         <v>79946</v>
@@ -10487,10 +10487,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>421655</v>
+        <v>421507</v>
       </c>
       <c r="R89" t="n">
-        <v>6787687</v>
+        <v>6788435</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10558,13 +10558,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095786</t>
+          <t>https://artportalen.se/Sighting/129095002</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129095862</v>
+        <v>129095786</v>
       </c>
       <c r="B90" t="n">
         <v>79946</v>
@@ -10599,10 +10599,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>421631</v>
+        <v>421655</v>
       </c>
       <c r="R90" t="n">
-        <v>6787723</v>
+        <v>6787687</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10670,13 +10670,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095862</t>
+          <t>https://artportalen.se/Sighting/129095786</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129095947</v>
+        <v>129095862</v>
       </c>
       <c r="B91" t="n">
         <v>79946</v>
@@ -10711,10 +10711,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>421617</v>
+        <v>421631</v>
       </c>
       <c r="R91" t="n">
-        <v>6787742</v>
+        <v>6787723</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10782,13 +10782,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095947</t>
+          <t>https://artportalen.se/Sighting/129095862</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129124051</v>
+        <v>129095947</v>
       </c>
       <c r="B92" t="n">
         <v>79946</v>
@@ -10819,14 +10819,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>421392</v>
+        <v>421617</v>
       </c>
       <c r="R92" t="n">
-        <v>6788226</v>
+        <v>6787742</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10883,24 +10883,24 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124051</t>
+          <t>https://artportalen.se/Sighting/129095947</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129124052</v>
+        <v>129124051</v>
       </c>
       <c r="B93" t="n">
         <v>79946</v>
@@ -10935,10 +10935,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>421391</v>
+        <v>421392</v>
       </c>
       <c r="R93" t="n">
-        <v>6788209</v>
+        <v>6788226</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11006,13 +11006,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124052</t>
+          <t>https://artportalen.se/Sighting/129124051</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129124053</v>
+        <v>129124052</v>
       </c>
       <c r="B94" t="n">
         <v>79946</v>
@@ -11047,10 +11047,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>421421</v>
+        <v>421391</v>
       </c>
       <c r="R94" t="n">
-        <v>6788216</v>
+        <v>6788209</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11118,13 +11118,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124053</t>
+          <t>https://artportalen.se/Sighting/129124052</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129124054</v>
+        <v>129124053</v>
       </c>
       <c r="B95" t="n">
         <v>79946</v>
@@ -11159,10 +11159,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>421423</v>
+        <v>421421</v>
       </c>
       <c r="R95" t="n">
-        <v>6788261</v>
+        <v>6788216</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11230,13 +11230,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124054</t>
+          <t>https://artportalen.se/Sighting/129124053</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129124055</v>
+        <v>129124054</v>
       </c>
       <c r="B96" t="n">
         <v>79946</v>
@@ -11271,10 +11271,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>421411</v>
+        <v>421423</v>
       </c>
       <c r="R96" t="n">
-        <v>6788356</v>
+        <v>6788261</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11342,13 +11342,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124055</t>
+          <t>https://artportalen.se/Sighting/129124054</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129124056</v>
+        <v>129124055</v>
       </c>
       <c r="B97" t="n">
         <v>79946</v>
@@ -11383,10 +11383,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>421343</v>
+        <v>421411</v>
       </c>
       <c r="R97" t="n">
-        <v>6788400</v>
+        <v>6788356</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11418,7 +11418,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11454,13 +11454,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124056</t>
+          <t>https://artportalen.se/Sighting/129124055</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129124057</v>
+        <v>129124056</v>
       </c>
       <c r="B98" t="n">
         <v>79946</v>
@@ -11495,10 +11495,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>421312</v>
+        <v>421343</v>
       </c>
       <c r="R98" t="n">
-        <v>6788393</v>
+        <v>6788400</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11530,7 +11530,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11566,13 +11566,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124057</t>
+          <t>https://artportalen.se/Sighting/129124056</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129124058</v>
+        <v>129124057</v>
       </c>
       <c r="B99" t="n">
         <v>79946</v>
@@ -11607,10 +11607,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>421246</v>
+        <v>421312</v>
       </c>
       <c r="R99" t="n">
-        <v>6788416</v>
+        <v>6788393</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11678,13 +11678,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124058</t>
+          <t>https://artportalen.se/Sighting/129124057</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129124059</v>
+        <v>129124058</v>
       </c>
       <c r="B100" t="n">
         <v>79946</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>421354</v>
+        <v>421246</v>
       </c>
       <c r="R100" t="n">
-        <v>6788463</v>
+        <v>6788416</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11790,13 +11790,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124059</t>
+          <t>https://artportalen.se/Sighting/129124058</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129124060</v>
+        <v>129124059</v>
       </c>
       <c r="B101" t="n">
         <v>79946</v>
@@ -11831,10 +11831,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>421338</v>
+        <v>421354</v>
       </c>
       <c r="R101" t="n">
-        <v>6788476</v>
+        <v>6788463</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11902,13 +11902,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124060</t>
+          <t>https://artportalen.se/Sighting/129124059</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129124061</v>
+        <v>129124060</v>
       </c>
       <c r="B102" t="n">
         <v>79946</v>
@@ -11943,10 +11943,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>421238</v>
+        <v>421338</v>
       </c>
       <c r="R102" t="n">
-        <v>6788555</v>
+        <v>6788476</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12014,13 +12014,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124061</t>
+          <t>https://artportalen.se/Sighting/129124060</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129124062</v>
+        <v>129124061</v>
       </c>
       <c r="B103" t="n">
         <v>79946</v>
@@ -12055,10 +12055,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>421395</v>
+        <v>421238</v>
       </c>
       <c r="R103" t="n">
-        <v>6788610</v>
+        <v>6788555</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12090,7 +12090,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12126,13 +12126,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124062</t>
+          <t>https://artportalen.se/Sighting/129124061</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129124063</v>
+        <v>129124062</v>
       </c>
       <c r="B104" t="n">
         <v>79946</v>
@@ -12167,10 +12167,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>421442</v>
+        <v>421395</v>
       </c>
       <c r="R104" t="n">
-        <v>6788613</v>
+        <v>6788610</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12202,7 +12202,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12212,7 +12212,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12238,13 +12238,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124063</t>
+          <t>https://artportalen.se/Sighting/129124062</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129124064</v>
+        <v>129124063</v>
       </c>
       <c r="B105" t="n">
         <v>79946</v>
@@ -12279,10 +12279,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>421501</v>
+        <v>421442</v>
       </c>
       <c r="R105" t="n">
-        <v>6788671</v>
+        <v>6788613</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12314,7 +12314,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12350,13 +12350,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124064</t>
+          <t>https://artportalen.se/Sighting/129124063</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129124065</v>
+        <v>129124064</v>
       </c>
       <c r="B106" t="n">
         <v>79946</v>
@@ -12391,10 +12391,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>421530</v>
+        <v>421501</v>
       </c>
       <c r="R106" t="n">
-        <v>6788679</v>
+        <v>6788671</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12436,7 +12436,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12462,13 +12462,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124065</t>
+          <t>https://artportalen.se/Sighting/129124064</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129124068</v>
+        <v>129124065</v>
       </c>
       <c r="B107" t="n">
         <v>79946</v>
@@ -12503,10 +12503,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>421675</v>
+        <v>421530</v>
       </c>
       <c r="R107" t="n">
-        <v>6787696</v>
+        <v>6788679</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12538,7 +12538,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12574,13 +12574,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124068</t>
+          <t>https://artportalen.se/Sighting/129124065</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129124069</v>
+        <v>129124068</v>
       </c>
       <c r="B108" t="n">
         <v>79946</v>
@@ -12615,10 +12615,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>421626</v>
+        <v>421675</v>
       </c>
       <c r="R108" t="n">
-        <v>6787879</v>
+        <v>6787696</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12686,13 +12686,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124069</t>
+          <t>https://artportalen.se/Sighting/129124068</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129124070</v>
+        <v>129124069</v>
       </c>
       <c r="B109" t="n">
         <v>79946</v>
@@ -12727,10 +12727,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>421616</v>
+        <v>421626</v>
       </c>
       <c r="R109" t="n">
-        <v>6787882</v>
+        <v>6787879</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12762,7 +12762,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12798,13 +12798,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124070</t>
+          <t>https://artportalen.se/Sighting/129124069</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129124071</v>
+        <v>129124070</v>
       </c>
       <c r="B110" t="n">
         <v>79946</v>
@@ -12839,10 +12839,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>421598</v>
+        <v>421616</v>
       </c>
       <c r="R110" t="n">
-        <v>6787863</v>
+        <v>6787882</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12910,13 +12910,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124071</t>
+          <t>https://artportalen.se/Sighting/129124070</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129124072</v>
+        <v>129124071</v>
       </c>
       <c r="B111" t="n">
         <v>79946</v>
@@ -12951,10 +12951,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>421591</v>
+        <v>421598</v>
       </c>
       <c r="R111" t="n">
-        <v>6787819</v>
+        <v>6787863</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12986,7 +12986,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13022,13 +13022,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124072</t>
+          <t>https://artportalen.se/Sighting/129124071</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129124073</v>
+        <v>129124072</v>
       </c>
       <c r="B112" t="n">
         <v>79946</v>
@@ -13063,10 +13063,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>421595</v>
+        <v>421591</v>
       </c>
       <c r="R112" t="n">
-        <v>6787823</v>
+        <v>6787819</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13134,56 +13134,51 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124073</t>
+          <t>https://artportalen.se/Sighting/129124072</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129094162</v>
+        <v>129124073</v>
       </c>
       <c r="B113" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>421499</v>
+        <v>421595</v>
       </c>
       <c r="R113" t="n">
-        <v>6788592</v>
+        <v>6787823</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13215,7 +13210,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13225,7 +13220,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13240,24 +13235,24 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094162</t>
+          <t>https://artportalen.se/Sighting/129124073</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129094242</v>
+        <v>129094162</v>
       </c>
       <c r="B114" t="n">
         <v>57950</v>
@@ -13297,10 +13292,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>421564</v>
+        <v>421499</v>
       </c>
       <c r="R114" t="n">
-        <v>6788544</v>
+        <v>6788592</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13368,13 +13363,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094242</t>
+          <t>https://artportalen.se/Sighting/129094162</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129094871</v>
+        <v>129094242</v>
       </c>
       <c r="B115" t="n">
         <v>57950</v>
@@ -13405,7 +13400,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -13414,10 +13409,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>421534</v>
+        <v>421564</v>
       </c>
       <c r="R115" t="n">
-        <v>6788452</v>
+        <v>6788544</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13485,13 +13480,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094871</t>
+          <t>https://artportalen.se/Sighting/129094242</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129124096</v>
+        <v>129094871</v>
       </c>
       <c r="B116" t="n">
         <v>57950</v>
@@ -13522,19 +13517,19 @@
       <c r="I116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>421596</v>
+        <v>421534</v>
       </c>
       <c r="R116" t="n">
-        <v>6787836</v>
+        <v>6788452</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13566,7 +13561,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13576,7 +13571,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13591,44 +13586,44 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124096</t>
+          <t>https://artportalen.se/Sighting/129094871</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129095090</v>
+        <v>129124096</v>
       </c>
       <c r="B117" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -13639,19 +13634,19 @@
       <c r="I117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>421500</v>
+        <v>421596</v>
       </c>
       <c r="R117" t="n">
-        <v>6788425</v>
+        <v>6787836</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13683,7 +13678,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13693,7 +13688,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13708,67 +13703,67 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095090</t>
+          <t>https://artportalen.se/Sighting/129124096</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129124088</v>
+        <v>129095090</v>
       </c>
       <c r="B118" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>421296</v>
+        <v>421500</v>
       </c>
       <c r="R118" t="n">
-        <v>6788608</v>
+        <v>6788425</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13800,7 +13795,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13810,7 +13805,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13825,27 +13820,27 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124088</t>
+          <t>https://artportalen.se/Sighting/129095090</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129095582</v>
+        <v>129124088</v>
       </c>
       <c r="B119" t="n">
-        <v>58327</v>
+        <v>57141</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13853,39 +13848,39 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>421342</v>
+        <v>421296</v>
       </c>
       <c r="R119" t="n">
-        <v>6788310</v>
+        <v>6788608</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13917,7 +13912,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13927,7 +13922,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13942,71 +13937,67 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095582</t>
+          <t>https://artportalen.se/Sighting/129124088</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>88280081</v>
+        <v>129095582</v>
       </c>
       <c r="B120" t="n">
-        <v>12703</v>
+        <v>58327</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>105850</v>
+        <v>103015</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Corticeus longulus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1827)</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>sållning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Hädbodarna, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>421414</v>
+        <v>421342</v>
       </c>
       <c r="R120" t="n">
-        <v>6788091</v>
+        <v>6788310</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14033,17 +14024,22 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Ett dött ex (torrt fragment) utanpå bark. Övriga arter: timmerman (kläckhål), barrträdlöpare och allmän barkplattbagge (larver), Phloenomus, troligen lapponica, Phloeopora testacea, Placusa, troligen depressa (många ex)</t>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14054,78 +14050,63 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>Gles tallskog på svag sydvästsluttning, delvis försumpad</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Nydöd tall 37 cm, gröna, gula, bruna och röda barr, med båda arter märgborrar</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars, Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY120" t="inlineStr">
-        <is>
-          <t>Insekter på tallved i Dalarna 2020 - 2021</t>
-        </is>
-      </c>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88280081</t>
+          <t>https://artportalen.se/Sighting/129095582</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>88280082</v>
+        <v>88280081</v>
       </c>
       <c r="B121" t="n">
-        <v>8455</v>
+        <v>12703</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
+        <v>105850</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Corticeus longulus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Gyllenhal, 1827)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>sållning</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -14174,7 +14155,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Gnagspår och fragment, tillsammans med större märgborre. Den mindre föredrar tydligt sydsidan, här ned till 120 cm från rot</t>
+          <t>Ett dött ex (torrt fragment) utanpå bark. Övriga arter: timmerman (kläckhål), barrträdlöpare och allmän barkplattbagge (larver), Phloenomus, troligen lapponica, Phloeopora testacea, Placusa, troligen depressa (många ex)</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14193,7 +14174,12 @@
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Nydöd tall 37 cm, gröna, gula, bruna och röda barr</t>
+          <t>Nydöd tall 37 cm, gröna, gula, bruna och röda barr, med båda arter märgborrar</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14214,13 +14200,13 @@
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88280082</t>
+          <t>https://artportalen.se/Sighting/88280081</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129093117</v>
+        <v>88280082</v>
       </c>
       <c r="B122" t="n">
         <v>8455</v>
@@ -14249,16 +14235,21 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Hädbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>421391</v>
+        <v>421414</v>
       </c>
       <c r="R122" t="n">
-        <v>6788314</v>
+        <v>6788091</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14285,22 +14276,17 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Gnagspår och fragment, tillsammans med större märgborre. Den mindre föredrar tydligt sydsidan, här ned till 120 cm från rot</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14311,28 +14297,42 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>Gles tallskog på svag sydvästsluttning, delvis försumpad</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Nydöd tall 37 cm, gröna, gula, bruna och röda barr</t>
+        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AY122" t="inlineStr"/>
+          <t>Lars-Ove Wikars, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>Insekter på tallved i Dalarna 2020 - 2021</t>
+        </is>
+      </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093117</t>
+          <t>https://artportalen.se/Sighting/88280082</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129093853</v>
+        <v>129093117</v>
       </c>
       <c r="B123" t="n">
         <v>8455</v>
@@ -14367,10 +14367,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>421371</v>
+        <v>421391</v>
       </c>
       <c r="R123" t="n">
-        <v>6788472</v>
+        <v>6788314</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14438,13 +14438,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093853</t>
+          <t>https://artportalen.se/Sighting/129093117</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129093945</v>
+        <v>129093853</v>
       </c>
       <c r="B124" t="n">
         <v>8455</v>
@@ -14479,10 +14479,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>421399</v>
+        <v>421371</v>
       </c>
       <c r="R124" t="n">
-        <v>6788487</v>
+        <v>6788472</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14550,13 +14550,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093945</t>
+          <t>https://artportalen.se/Sighting/129093853</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129094196</v>
+        <v>129093945</v>
       </c>
       <c r="B125" t="n">
         <v>8455</v>
@@ -14591,10 +14591,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>421526</v>
+        <v>421399</v>
       </c>
       <c r="R125" t="n">
-        <v>6788587</v>
+        <v>6788487</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14662,13 +14662,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094196</t>
+          <t>https://artportalen.se/Sighting/129093945</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129094249</v>
+        <v>129094196</v>
       </c>
       <c r="B126" t="n">
         <v>8455</v>
@@ -14703,10 +14703,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>421564</v>
+        <v>421526</v>
       </c>
       <c r="R126" t="n">
-        <v>6788544</v>
+        <v>6788587</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14774,13 +14774,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094249</t>
+          <t>https://artportalen.se/Sighting/129094196</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129124106</v>
+        <v>129094249</v>
       </c>
       <c r="B127" t="n">
         <v>8455</v>
@@ -14809,21 +14809,16 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>421574</v>
+        <v>421564</v>
       </c>
       <c r="R127" t="n">
-        <v>6788374</v>
+        <v>6788544</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14855,7 +14850,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14865,7 +14860,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14880,24 +14875,24 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124106</t>
+          <t>https://artportalen.se/Sighting/129094249</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129124107</v>
+        <v>129124106</v>
       </c>
       <c r="B128" t="n">
         <v>8455</v>
@@ -14928,7 +14923,7 @@
       <c r="I128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -14937,10 +14932,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>421451</v>
+        <v>421574</v>
       </c>
       <c r="R128" t="n">
-        <v>6788307</v>
+        <v>6788374</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14972,7 +14967,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14982,7 +14977,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15008,13 +15003,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124107</t>
+          <t>https://artportalen.se/Sighting/129124106</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129124108</v>
+        <v>129124107</v>
       </c>
       <c r="B129" t="n">
         <v>8455</v>
@@ -15054,10 +15049,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>421362</v>
+        <v>421451</v>
       </c>
       <c r="R129" t="n">
-        <v>6788387</v>
+        <v>6788307</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15089,7 +15084,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15099,7 +15094,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15125,13 +15120,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124108</t>
+          <t>https://artportalen.se/Sighting/129124107</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129124109</v>
+        <v>129124108</v>
       </c>
       <c r="B130" t="n">
         <v>8455</v>
@@ -15171,10 +15166,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>421325</v>
+        <v>421362</v>
       </c>
       <c r="R130" t="n">
-        <v>6788393</v>
+        <v>6788387</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15206,7 +15201,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15216,7 +15211,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15242,13 +15237,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124109</t>
+          <t>https://artportalen.se/Sighting/129124108</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129124110</v>
+        <v>129124109</v>
       </c>
       <c r="B131" t="n">
         <v>8455</v>
@@ -15288,10 +15283,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>421271</v>
+        <v>421325</v>
       </c>
       <c r="R131" t="n">
-        <v>6788430</v>
+        <v>6788393</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15323,7 +15318,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15333,7 +15328,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15359,13 +15354,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124110</t>
+          <t>https://artportalen.se/Sighting/129124109</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129124111</v>
+        <v>129124110</v>
       </c>
       <c r="B132" t="n">
         <v>8455</v>
@@ -15405,10 +15400,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>421315</v>
+        <v>421271</v>
       </c>
       <c r="R132" t="n">
-        <v>6788532</v>
+        <v>6788430</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15440,7 +15435,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15450,7 +15445,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15476,13 +15471,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124111</t>
+          <t>https://artportalen.se/Sighting/129124110</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129124112</v>
+        <v>129124111</v>
       </c>
       <c r="B133" t="n">
         <v>8455</v>
@@ -15522,10 +15517,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>421293</v>
+        <v>421315</v>
       </c>
       <c r="R133" t="n">
-        <v>6788551</v>
+        <v>6788532</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15557,7 +15552,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15567,7 +15562,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15593,13 +15588,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124112</t>
+          <t>https://artportalen.se/Sighting/129124111</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129124114</v>
+        <v>129124112</v>
       </c>
       <c r="B134" t="n">
         <v>8455</v>
@@ -15639,10 +15634,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>421399</v>
+        <v>421293</v>
       </c>
       <c r="R134" t="n">
-        <v>6788567</v>
+        <v>6788551</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15674,7 +15669,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15684,7 +15679,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15710,13 +15705,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124114</t>
+          <t>https://artportalen.se/Sighting/129124112</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129124115</v>
+        <v>129124114</v>
       </c>
       <c r="B135" t="n">
         <v>8455</v>
@@ -15756,10 +15751,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>421608</v>
+        <v>421399</v>
       </c>
       <c r="R135" t="n">
-        <v>6788661</v>
+        <v>6788567</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15791,7 +15786,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15801,7 +15796,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15827,13 +15822,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124115</t>
+          <t>https://artportalen.se/Sighting/129124114</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129124116</v>
+        <v>129124115</v>
       </c>
       <c r="B136" t="n">
         <v>8455</v>
@@ -15873,10 +15868,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>421615</v>
+        <v>421608</v>
       </c>
       <c r="R136" t="n">
-        <v>6788580</v>
+        <v>6788661</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15908,7 +15903,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15918,7 +15913,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15944,13 +15939,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124116</t>
+          <t>https://artportalen.se/Sighting/129124115</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129124117</v>
+        <v>129124116</v>
       </c>
       <c r="B137" t="n">
         <v>8455</v>
@@ -15990,10 +15985,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>421611</v>
+        <v>421615</v>
       </c>
       <c r="R137" t="n">
-        <v>6788482</v>
+        <v>6788580</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16025,7 +16020,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16035,7 +16030,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16061,13 +16056,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124117</t>
+          <t>https://artportalen.se/Sighting/129124116</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129124119</v>
+        <v>129124117</v>
       </c>
       <c r="B138" t="n">
         <v>8455</v>
@@ -16107,10 +16102,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>421653</v>
+        <v>421611</v>
       </c>
       <c r="R138" t="n">
-        <v>6788387</v>
+        <v>6788482</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16142,7 +16137,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16152,7 +16147,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16178,13 +16173,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124119</t>
+          <t>https://artportalen.se/Sighting/129124117</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129124120</v>
+        <v>129124119</v>
       </c>
       <c r="B139" t="n">
         <v>8455</v>
@@ -16224,10 +16219,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>421520</v>
+        <v>421653</v>
       </c>
       <c r="R139" t="n">
-        <v>6788366</v>
+        <v>6788387</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16259,7 +16254,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16269,7 +16264,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16295,13 +16290,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124120</t>
+          <t>https://artportalen.se/Sighting/129124119</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129124121</v>
+        <v>129124120</v>
       </c>
       <c r="B140" t="n">
         <v>8455</v>
@@ -16341,10 +16336,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>421524</v>
+        <v>421520</v>
       </c>
       <c r="R140" t="n">
-        <v>6788399</v>
+        <v>6788366</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16376,7 +16371,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16386,7 +16381,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16412,13 +16407,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124121</t>
+          <t>https://artportalen.se/Sighting/129124120</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129124122</v>
+        <v>129124121</v>
       </c>
       <c r="B141" t="n">
         <v>8455</v>
@@ -16458,10 +16453,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>421477</v>
+        <v>421524</v>
       </c>
       <c r="R141" t="n">
-        <v>6788422</v>
+        <v>6788399</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16493,7 +16488,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16503,7 +16498,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16529,13 +16524,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124122</t>
+          <t>https://artportalen.se/Sighting/129124121</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129124123</v>
+        <v>129124122</v>
       </c>
       <c r="B142" t="n">
         <v>8455</v>
@@ -16575,10 +16570,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>421446</v>
+        <v>421477</v>
       </c>
       <c r="R142" t="n">
-        <v>6788421</v>
+        <v>6788422</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16610,7 +16605,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16620,7 +16615,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16646,13 +16641,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124123</t>
+          <t>https://artportalen.se/Sighting/129124122</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129124124</v>
+        <v>129124123</v>
       </c>
       <c r="B143" t="n">
         <v>8455</v>
@@ -16692,10 +16687,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>421440</v>
+        <v>421446</v>
       </c>
       <c r="R143" t="n">
-        <v>6788409</v>
+        <v>6788421</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16727,7 +16722,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16737,7 +16732,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16763,13 +16758,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124124</t>
+          <t>https://artportalen.se/Sighting/129124123</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129124125</v>
+        <v>129124124</v>
       </c>
       <c r="B144" t="n">
         <v>8455</v>
@@ -16809,10 +16804,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>421369</v>
+        <v>421440</v>
       </c>
       <c r="R144" t="n">
-        <v>6788395</v>
+        <v>6788409</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16844,7 +16839,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16854,7 +16849,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16880,13 +16875,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124125</t>
+          <t>https://artportalen.se/Sighting/129124124</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129124126</v>
+        <v>129124125</v>
       </c>
       <c r="B145" t="n">
         <v>8455</v>
@@ -16926,10 +16921,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>421654</v>
+        <v>421369</v>
       </c>
       <c r="R145" t="n">
-        <v>6787690</v>
+        <v>6788395</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16961,7 +16956,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16971,7 +16966,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16997,13 +16992,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124126</t>
+          <t>https://artportalen.se/Sighting/129124125</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129124127</v>
+        <v>129124126</v>
       </c>
       <c r="B146" t="n">
         <v>8455</v>
@@ -17043,10 +17038,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>421630</v>
+        <v>421654</v>
       </c>
       <c r="R146" t="n">
-        <v>6787815</v>
+        <v>6787690</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17078,7 +17073,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17088,7 +17083,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17114,51 +17109,56 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124127</t>
+          <t>https://artportalen.se/Sighting/129124126</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129095730</v>
+        <v>129124127</v>
       </c>
       <c r="B147" t="n">
-        <v>79085</v>
+        <v>8455</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>421655</v>
+        <v>421630</v>
       </c>
       <c r="R147" t="n">
-        <v>6787687</v>
+        <v>6787815</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17190,7 +17190,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17200,7 +17200,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17215,24 +17215,24 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095730</t>
+          <t>https://artportalen.se/Sighting/129124127</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129124103</v>
+        <v>129095730</v>
       </c>
       <c r="B148" t="n">
         <v>79085</v>
@@ -17263,14 +17263,14 @@
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>421618</v>
+        <v>421655</v>
       </c>
       <c r="R148" t="n">
-        <v>6787832</v>
+        <v>6787687</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17327,24 +17327,24 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124103</t>
+          <t>https://artportalen.se/Sighting/129095730</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129124128</v>
+        <v>129124103</v>
       </c>
       <c r="B149" t="n">
         <v>79085</v>
@@ -17379,10 +17379,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>421391</v>
+        <v>421618</v>
       </c>
       <c r="R149" t="n">
-        <v>6788209</v>
+        <v>6787832</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17424,7 +17424,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17450,13 +17450,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124128</t>
+          <t>https://artportalen.se/Sighting/129124103</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129124129</v>
+        <v>129124128</v>
       </c>
       <c r="B150" t="n">
         <v>79085</v>
@@ -17491,10 +17491,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>421292</v>
+        <v>421391</v>
       </c>
       <c r="R150" t="n">
-        <v>6788456</v>
+        <v>6788209</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17526,7 +17526,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17536,7 +17536,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17562,13 +17562,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124129</t>
+          <t>https://artportalen.se/Sighting/129124128</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129124130</v>
+        <v>129124129</v>
       </c>
       <c r="B151" t="n">
         <v>79085</v>
@@ -17603,10 +17603,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>421354</v>
+        <v>421292</v>
       </c>
       <c r="R151" t="n">
-        <v>6788463</v>
+        <v>6788456</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17648,7 +17648,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17674,13 +17674,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124130</t>
+          <t>https://artportalen.se/Sighting/129124129</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129124131</v>
+        <v>129124130</v>
       </c>
       <c r="B152" t="n">
         <v>79085</v>
@@ -17715,10 +17715,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>421659</v>
+        <v>421354</v>
       </c>
       <c r="R152" t="n">
-        <v>6787750</v>
+        <v>6788463</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17760,7 +17760,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17786,13 +17786,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124131</t>
+          <t>https://artportalen.se/Sighting/129124130</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129124132</v>
+        <v>129124131</v>
       </c>
       <c r="B153" t="n">
         <v>79085</v>
@@ -17827,10 +17827,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>421649</v>
+        <v>421659</v>
       </c>
       <c r="R153" t="n">
-        <v>6787778</v>
+        <v>6787750</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17862,7 +17862,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17872,7 +17872,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17898,13 +17898,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124132</t>
+          <t>https://artportalen.se/Sighting/129124131</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129124133</v>
+        <v>129124132</v>
       </c>
       <c r="B154" t="n">
         <v>79085</v>
@@ -17939,10 +17939,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>421633</v>
+        <v>421649</v>
       </c>
       <c r="R154" t="n">
-        <v>6787841</v>
+        <v>6787778</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17974,7 +17974,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17984,7 +17984,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18010,13 +18010,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124133</t>
+          <t>https://artportalen.se/Sighting/129124132</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129124134</v>
+        <v>129124133</v>
       </c>
       <c r="B155" t="n">
         <v>79085</v>
@@ -18051,10 +18051,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>421616</v>
+        <v>421633</v>
       </c>
       <c r="R155" t="n">
-        <v>6787882</v>
+        <v>6787841</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18096,7 +18096,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18122,13 +18122,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124134</t>
+          <t>https://artportalen.se/Sighting/129124133</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129124135</v>
+        <v>129124134</v>
       </c>
       <c r="B156" t="n">
         <v>79085</v>
@@ -18163,10 +18163,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>421594</v>
+        <v>421616</v>
       </c>
       <c r="R156" t="n">
-        <v>6787870</v>
+        <v>6787882</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18198,7 +18198,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18208,7 +18208,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18234,13 +18234,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124135</t>
+          <t>https://artportalen.se/Sighting/129124134</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129124136</v>
+        <v>129124135</v>
       </c>
       <c r="B157" t="n">
         <v>79085</v>
@@ -18275,10 +18275,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>421598</v>
+        <v>421594</v>
       </c>
       <c r="R157" t="n">
-        <v>6787834</v>
+        <v>6787870</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18310,7 +18310,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18346,16 +18346,16 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124136</t>
+          <t>https://artportalen.se/Sighting/129124135</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129093598</v>
+        <v>129124136</v>
       </c>
       <c r="B158" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18363,34 +18363,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>421371</v>
+        <v>421598</v>
       </c>
       <c r="R158" t="n">
-        <v>6788472</v>
+        <v>6787834</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18432,7 +18432,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18447,24 +18447,24 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093598</t>
+          <t>https://artportalen.se/Sighting/129124136</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129094076</v>
+        <v>129093598</v>
       </c>
       <c r="B159" t="n">
         <v>79917</v>
@@ -18499,10 +18499,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>421379</v>
+        <v>421371</v>
       </c>
       <c r="R159" t="n">
-        <v>6788540</v>
+        <v>6788472</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18570,13 +18570,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094076</t>
+          <t>https://artportalen.se/Sighting/129093598</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129094542</v>
+        <v>129094076</v>
       </c>
       <c r="B160" t="n">
         <v>79917</v>
@@ -18611,10 +18611,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>421564</v>
+        <v>421379</v>
       </c>
       <c r="R160" t="n">
-        <v>6788544</v>
+        <v>6788540</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18682,13 +18682,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094542</t>
+          <t>https://artportalen.se/Sighting/129094076</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129094943</v>
+        <v>129094542</v>
       </c>
       <c r="B161" t="n">
         <v>79917</v>
@@ -18723,10 +18723,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>421534</v>
+        <v>421564</v>
       </c>
       <c r="R161" t="n">
-        <v>6788452</v>
+        <v>6788544</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18794,13 +18794,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094943</t>
+          <t>https://artportalen.se/Sighting/129094542</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129095743</v>
+        <v>129094943</v>
       </c>
       <c r="B162" t="n">
         <v>79917</v>
@@ -18835,10 +18835,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>421655</v>
+        <v>421534</v>
       </c>
       <c r="R162" t="n">
-        <v>6787687</v>
+        <v>6788452</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18906,13 +18906,13 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095743</t>
+          <t>https://artportalen.se/Sighting/129094943</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129095886</v>
+        <v>129095743</v>
       </c>
       <c r="B163" t="n">
         <v>79917</v>
@@ -18947,10 +18947,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>421623</v>
+        <v>421655</v>
       </c>
       <c r="R163" t="n">
-        <v>6787731</v>
+        <v>6787687</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19018,13 +19018,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095886</t>
+          <t>https://artportalen.se/Sighting/129095743</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129095952</v>
+        <v>129095886</v>
       </c>
       <c r="B164" t="n">
         <v>79917</v>
@@ -19059,10 +19059,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>421617</v>
+        <v>421623</v>
       </c>
       <c r="R164" t="n">
-        <v>6787742</v>
+        <v>6787731</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19130,13 +19130,13 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095952</t>
+          <t>https://artportalen.se/Sighting/129095886</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129124074</v>
+        <v>129095952</v>
       </c>
       <c r="B165" t="n">
         <v>79917</v>
@@ -19167,14 +19167,14 @@
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>421236</v>
+        <v>421617</v>
       </c>
       <c r="R165" t="n">
-        <v>6788559</v>
+        <v>6787742</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19206,7 +19206,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19216,12 +19216,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>På stubbe med 6 brandljud</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19236,24 +19231,24 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124074</t>
+          <t>https://artportalen.se/Sighting/129095952</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129124075</v>
+        <v>129124074</v>
       </c>
       <c r="B166" t="n">
         <v>79917</v>
@@ -19288,10 +19283,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>421449</v>
+        <v>421236</v>
       </c>
       <c r="R166" t="n">
-        <v>6788278</v>
+        <v>6788559</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19323,7 +19318,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19333,7 +19328,12 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>På stubbe med 6 brandljud</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19359,13 +19359,13 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124075</t>
+          <t>https://artportalen.se/Sighting/129124074</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129124076</v>
+        <v>129124075</v>
       </c>
       <c r="B167" t="n">
         <v>79917</v>
@@ -19400,10 +19400,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>421240</v>
+        <v>421449</v>
       </c>
       <c r="R167" t="n">
-        <v>6788558</v>
+        <v>6788278</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19435,7 +19435,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19445,7 +19445,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19471,13 +19471,13 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124076</t>
+          <t>https://artportalen.se/Sighting/129124075</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129124077</v>
+        <v>129124076</v>
       </c>
       <c r="B168" t="n">
         <v>79917</v>
@@ -19512,10 +19512,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>421633</v>
+        <v>421240</v>
       </c>
       <c r="R168" t="n">
-        <v>6788617</v>
+        <v>6788558</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19583,13 +19583,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124077</t>
+          <t>https://artportalen.se/Sighting/129124076</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129124078</v>
+        <v>129124077</v>
       </c>
       <c r="B169" t="n">
         <v>79917</v>
@@ -19624,10 +19624,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>421640</v>
+        <v>421633</v>
       </c>
       <c r="R169" t="n">
-        <v>6788394</v>
+        <v>6788617</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19695,13 +19695,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124078</t>
+          <t>https://artportalen.se/Sighting/129124077</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129124079</v>
+        <v>129124078</v>
       </c>
       <c r="B170" t="n">
         <v>79917</v>
@@ -19736,10 +19736,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>421652</v>
+        <v>421640</v>
       </c>
       <c r="R170" t="n">
-        <v>6787685</v>
+        <v>6788394</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19771,7 +19771,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -19781,7 +19781,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19807,13 +19807,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124079</t>
+          <t>https://artportalen.se/Sighting/129124078</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129124080</v>
+        <v>129124079</v>
       </c>
       <c r="B171" t="n">
         <v>79917</v>
@@ -19848,10 +19848,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>421633</v>
+        <v>421652</v>
       </c>
       <c r="R171" t="n">
-        <v>6787841</v>
+        <v>6787685</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19919,13 +19919,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124080</t>
+          <t>https://artportalen.se/Sighting/129124079</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129124081</v>
+        <v>129124080</v>
       </c>
       <c r="B172" t="n">
         <v>79917</v>
@@ -19960,10 +19960,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>421592</v>
+        <v>421633</v>
       </c>
       <c r="R172" t="n">
-        <v>6787842</v>
+        <v>6787841</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19995,7 +19995,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -20005,7 +20005,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20031,13 +20031,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124081</t>
+          <t>https://artportalen.se/Sighting/129124080</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129124082</v>
+        <v>129124081</v>
       </c>
       <c r="B173" t="n">
         <v>79917</v>
@@ -20072,10 +20072,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>421601</v>
+        <v>421592</v>
       </c>
       <c r="R173" t="n">
-        <v>6787830</v>
+        <v>6787842</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20107,7 +20107,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -20117,7 +20117,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20143,13 +20143,13 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124082</t>
+          <t>https://artportalen.se/Sighting/129124081</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129124083</v>
+        <v>129124082</v>
       </c>
       <c r="B174" t="n">
         <v>79917</v>
@@ -20184,10 +20184,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>421598</v>
+        <v>421601</v>
       </c>
       <c r="R174" t="n">
-        <v>6787829</v>
+        <v>6787830</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20255,13 +20255,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124083</t>
+          <t>https://artportalen.se/Sighting/129124082</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129124084</v>
+        <v>129124083</v>
       </c>
       <c r="B175" t="n">
         <v>79917</v>
@@ -20296,10 +20296,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>421591</v>
+        <v>421598</v>
       </c>
       <c r="R175" t="n">
-        <v>6787819</v>
+        <v>6787829</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -20341,7 +20341,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20367,13 +20367,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124084</t>
+          <t>https://artportalen.se/Sighting/129124083</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129124085</v>
+        <v>129124084</v>
       </c>
       <c r="B176" t="n">
         <v>79917</v>
@@ -20408,10 +20408,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>421622</v>
+        <v>421591</v>
       </c>
       <c r="R176" t="n">
-        <v>6787726</v>
+        <v>6787819</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20479,16 +20479,16 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124085</t>
+          <t>https://artportalen.se/Sighting/129124084</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129124091</v>
+        <v>129124085</v>
       </c>
       <c r="B177" t="n">
-        <v>79350</v>
+        <v>79917</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20496,21 +20496,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -20520,10 +20520,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>421255</v>
+        <v>421622</v>
       </c>
       <c r="R177" t="n">
-        <v>6788442</v>
+        <v>6787726</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20555,7 +20555,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -20565,7 +20565,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20591,16 +20591,16 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124091</t>
+          <t>https://artportalen.se/Sighting/129124085</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>137209425</v>
+        <v>129124091</v>
       </c>
       <c r="B178" t="n">
-        <v>79511</v>
+        <v>79350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20632,13 +20632,13 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>421202</v>
+        <v>421255</v>
       </c>
       <c r="R178" t="n">
-        <v>6788653</v>
+        <v>6788442</v>
       </c>
       <c r="S178" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -20662,22 +20662,22 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20692,16 +20692,128 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124091</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>137209425</v>
+      </c>
+      <c r="B179" t="n">
+        <v>79524</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Blåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>421202</v>
+      </c>
+      <c r="R179" t="n">
+        <v>6788653</v>
+      </c>
+      <c r="S179" t="n">
+        <v>9</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT179" t="inlineStr"/>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137209425</t>
         </is>
@@ -20886,6 +20998,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -8551,7 +8551,7 @@
         <v>137237604</v>
       </c>
       <c r="B72" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>137209425</v>
       </c>
       <c r="B179" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -8551,7 +8551,7 @@
         <v>137237604</v>
       </c>
       <c r="B72" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>137209425</v>
       </c>
       <c r="B179" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -8551,7 +8551,7 @@
         <v>137237604</v>
       </c>
       <c r="B72" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>137209425</v>
       </c>
       <c r="B179" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ179"/>
+  <dimension ref="A1:AZ181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8551,7 +8551,7 @@
         <v>137237604</v>
       </c>
       <c r="B72" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -17232,48 +17232,49 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129095730</v>
+        <v>137403526</v>
       </c>
       <c r="B148" t="n">
-        <v>79085</v>
+        <v>8470</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>421655</v>
+        <v>421205</v>
       </c>
       <c r="R148" t="n">
-        <v>6787687</v>
+        <v>6788671</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17297,22 +17298,22 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17327,24 +17328,24 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist, Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095730</t>
+          <t>https://artportalen.se/Sighting/137403526</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129124103</v>
+        <v>129095730</v>
       </c>
       <c r="B149" t="n">
         <v>79085</v>
@@ -17375,14 +17376,14 @@
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>421618</v>
+        <v>421655</v>
       </c>
       <c r="R149" t="n">
-        <v>6787832</v>
+        <v>6787687</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17414,7 +17415,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17424,7 +17425,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17439,24 +17440,24 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124103</t>
+          <t>https://artportalen.se/Sighting/129095730</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129124128</v>
+        <v>129124103</v>
       </c>
       <c r="B150" t="n">
         <v>79085</v>
@@ -17491,10 +17492,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>421391</v>
+        <v>421618</v>
       </c>
       <c r="R150" t="n">
-        <v>6788209</v>
+        <v>6787832</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17526,7 +17527,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17536,7 +17537,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17562,13 +17563,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124128</t>
+          <t>https://artportalen.se/Sighting/129124103</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129124129</v>
+        <v>129124128</v>
       </c>
       <c r="B151" t="n">
         <v>79085</v>
@@ -17603,10 +17604,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>421292</v>
+        <v>421391</v>
       </c>
       <c r="R151" t="n">
-        <v>6788456</v>
+        <v>6788209</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17638,7 +17639,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17648,7 +17649,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17674,13 +17675,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124129</t>
+          <t>https://artportalen.se/Sighting/129124128</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129124130</v>
+        <v>129124129</v>
       </c>
       <c r="B152" t="n">
         <v>79085</v>
@@ -17715,10 +17716,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>421354</v>
+        <v>421292</v>
       </c>
       <c r="R152" t="n">
-        <v>6788463</v>
+        <v>6788456</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17750,7 +17751,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17760,7 +17761,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17786,13 +17787,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124130</t>
+          <t>https://artportalen.se/Sighting/129124129</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129124131</v>
+        <v>129124130</v>
       </c>
       <c r="B153" t="n">
         <v>79085</v>
@@ -17827,10 +17828,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>421659</v>
+        <v>421354</v>
       </c>
       <c r="R153" t="n">
-        <v>6787750</v>
+        <v>6788463</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17862,7 +17863,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17872,7 +17873,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17898,13 +17899,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124131</t>
+          <t>https://artportalen.se/Sighting/129124130</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129124132</v>
+        <v>129124131</v>
       </c>
       <c r="B154" t="n">
         <v>79085</v>
@@ -17939,10 +17940,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>421649</v>
+        <v>421659</v>
       </c>
       <c r="R154" t="n">
-        <v>6787778</v>
+        <v>6787750</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17974,7 +17975,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17984,7 +17985,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18010,13 +18011,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124132</t>
+          <t>https://artportalen.se/Sighting/129124131</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129124133</v>
+        <v>129124132</v>
       </c>
       <c r="B155" t="n">
         <v>79085</v>
@@ -18051,10 +18052,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>421633</v>
+        <v>421649</v>
       </c>
       <c r="R155" t="n">
-        <v>6787841</v>
+        <v>6787778</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18086,7 +18087,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18096,7 +18097,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18122,13 +18123,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124133</t>
+          <t>https://artportalen.se/Sighting/129124132</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129124134</v>
+        <v>129124133</v>
       </c>
       <c r="B156" t="n">
         <v>79085</v>
@@ -18163,10 +18164,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>421616</v>
+        <v>421633</v>
       </c>
       <c r="R156" t="n">
-        <v>6787882</v>
+        <v>6787841</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18198,7 +18199,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18208,7 +18209,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18234,13 +18235,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124134</t>
+          <t>https://artportalen.se/Sighting/129124133</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129124135</v>
+        <v>129124134</v>
       </c>
       <c r="B157" t="n">
         <v>79085</v>
@@ -18275,10 +18276,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>421594</v>
+        <v>421616</v>
       </c>
       <c r="R157" t="n">
-        <v>6787870</v>
+        <v>6787882</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18310,7 +18311,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18320,7 +18321,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18346,13 +18347,13 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124135</t>
+          <t>https://artportalen.se/Sighting/129124134</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129124136</v>
+        <v>129124135</v>
       </c>
       <c r="B158" t="n">
         <v>79085</v>
@@ -18387,10 +18388,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>421598</v>
+        <v>421594</v>
       </c>
       <c r="R158" t="n">
-        <v>6787834</v>
+        <v>6787870</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18422,7 +18423,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18432,7 +18433,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18458,16 +18459,16 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124136</t>
+          <t>https://artportalen.se/Sighting/129124135</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129093598</v>
+        <v>129124136</v>
       </c>
       <c r="B159" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18475,34 +18476,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>421371</v>
+        <v>421598</v>
       </c>
       <c r="R159" t="n">
-        <v>6788472</v>
+        <v>6787834</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18534,7 +18535,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18544,7 +18545,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18559,24 +18560,24 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093598</t>
+          <t>https://artportalen.se/Sighting/129124136</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129094076</v>
+        <v>129093598</v>
       </c>
       <c r="B160" t="n">
         <v>79917</v>
@@ -18611,10 +18612,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>421379</v>
+        <v>421371</v>
       </c>
       <c r="R160" t="n">
-        <v>6788540</v>
+        <v>6788472</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18682,13 +18683,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094076</t>
+          <t>https://artportalen.se/Sighting/129093598</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129094542</v>
+        <v>129094076</v>
       </c>
       <c r="B161" t="n">
         <v>79917</v>
@@ -18723,10 +18724,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>421564</v>
+        <v>421379</v>
       </c>
       <c r="R161" t="n">
-        <v>6788544</v>
+        <v>6788540</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18794,13 +18795,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094542</t>
+          <t>https://artportalen.se/Sighting/129094076</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129094943</v>
+        <v>129094542</v>
       </c>
       <c r="B162" t="n">
         <v>79917</v>
@@ -18835,10 +18836,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>421534</v>
+        <v>421564</v>
       </c>
       <c r="R162" t="n">
-        <v>6788452</v>
+        <v>6788544</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18906,13 +18907,13 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094943</t>
+          <t>https://artportalen.se/Sighting/129094542</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129095743</v>
+        <v>129094943</v>
       </c>
       <c r="B163" t="n">
         <v>79917</v>
@@ -18947,10 +18948,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>421655</v>
+        <v>421534</v>
       </c>
       <c r="R163" t="n">
-        <v>6787687</v>
+        <v>6788452</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19018,13 +19019,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095743</t>
+          <t>https://artportalen.se/Sighting/129094943</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129095886</v>
+        <v>129095743</v>
       </c>
       <c r="B164" t="n">
         <v>79917</v>
@@ -19059,10 +19060,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>421623</v>
+        <v>421655</v>
       </c>
       <c r="R164" t="n">
-        <v>6787731</v>
+        <v>6787687</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19130,13 +19131,13 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095886</t>
+          <t>https://artportalen.se/Sighting/129095743</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129095952</v>
+        <v>129095886</v>
       </c>
       <c r="B165" t="n">
         <v>79917</v>
@@ -19171,10 +19172,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>421617</v>
+        <v>421623</v>
       </c>
       <c r="R165" t="n">
-        <v>6787742</v>
+        <v>6787731</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19242,13 +19243,13 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095952</t>
+          <t>https://artportalen.se/Sighting/129095886</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129124074</v>
+        <v>129095952</v>
       </c>
       <c r="B166" t="n">
         <v>79917</v>
@@ -19279,14 +19280,14 @@
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>421236</v>
+        <v>421617</v>
       </c>
       <c r="R166" t="n">
-        <v>6788559</v>
+        <v>6787742</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19318,7 +19319,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19328,12 +19329,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>På stubbe med 6 brandljud</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19348,24 +19344,24 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124074</t>
+          <t>https://artportalen.se/Sighting/129095952</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129124075</v>
+        <v>129124074</v>
       </c>
       <c r="B167" t="n">
         <v>79917</v>
@@ -19400,10 +19396,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>421449</v>
+        <v>421236</v>
       </c>
       <c r="R167" t="n">
-        <v>6788278</v>
+        <v>6788559</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19435,7 +19431,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19445,7 +19441,12 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>På stubbe med 6 brandljud</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19471,13 +19472,13 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124075</t>
+          <t>https://artportalen.se/Sighting/129124074</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129124076</v>
+        <v>129124075</v>
       </c>
       <c r="B168" t="n">
         <v>79917</v>
@@ -19512,10 +19513,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>421240</v>
+        <v>421449</v>
       </c>
       <c r="R168" t="n">
-        <v>6788558</v>
+        <v>6788278</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19547,7 +19548,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -19557,7 +19558,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19583,13 +19584,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124076</t>
+          <t>https://artportalen.se/Sighting/129124075</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129124077</v>
+        <v>129124076</v>
       </c>
       <c r="B169" t="n">
         <v>79917</v>
@@ -19624,10 +19625,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>421633</v>
+        <v>421240</v>
       </c>
       <c r="R169" t="n">
-        <v>6788617</v>
+        <v>6788558</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19659,7 +19660,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -19669,7 +19670,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19695,13 +19696,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124077</t>
+          <t>https://artportalen.se/Sighting/129124076</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129124078</v>
+        <v>129124077</v>
       </c>
       <c r="B170" t="n">
         <v>79917</v>
@@ -19736,10 +19737,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>421640</v>
+        <v>421633</v>
       </c>
       <c r="R170" t="n">
-        <v>6788394</v>
+        <v>6788617</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19771,7 +19772,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -19781,7 +19782,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19807,13 +19808,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124078</t>
+          <t>https://artportalen.se/Sighting/129124077</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129124079</v>
+        <v>129124078</v>
       </c>
       <c r="B171" t="n">
         <v>79917</v>
@@ -19848,10 +19849,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>421652</v>
+        <v>421640</v>
       </c>
       <c r="R171" t="n">
-        <v>6787685</v>
+        <v>6788394</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19883,7 +19884,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19893,7 +19894,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19919,13 +19920,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124079</t>
+          <t>https://artportalen.se/Sighting/129124078</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129124080</v>
+        <v>129124079</v>
       </c>
       <c r="B172" t="n">
         <v>79917</v>
@@ -19960,10 +19961,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>421633</v>
+        <v>421652</v>
       </c>
       <c r="R172" t="n">
-        <v>6787841</v>
+        <v>6787685</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19995,7 +19996,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -20005,7 +20006,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20031,13 +20032,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124080</t>
+          <t>https://artportalen.se/Sighting/129124079</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129124081</v>
+        <v>129124080</v>
       </c>
       <c r="B173" t="n">
         <v>79917</v>
@@ -20072,10 +20073,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>421592</v>
+        <v>421633</v>
       </c>
       <c r="R173" t="n">
-        <v>6787842</v>
+        <v>6787841</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20107,7 +20108,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -20117,7 +20118,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20143,13 +20144,13 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124081</t>
+          <t>https://artportalen.se/Sighting/129124080</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129124082</v>
+        <v>129124081</v>
       </c>
       <c r="B174" t="n">
         <v>79917</v>
@@ -20184,10 +20185,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>421601</v>
+        <v>421592</v>
       </c>
       <c r="R174" t="n">
-        <v>6787830</v>
+        <v>6787842</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20219,7 +20220,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -20229,7 +20230,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20255,13 +20256,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124082</t>
+          <t>https://artportalen.se/Sighting/129124081</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129124083</v>
+        <v>129124082</v>
       </c>
       <c r="B175" t="n">
         <v>79917</v>
@@ -20296,10 +20297,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>421598</v>
+        <v>421601</v>
       </c>
       <c r="R175" t="n">
-        <v>6787829</v>
+        <v>6787830</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20367,13 +20368,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124083</t>
+          <t>https://artportalen.se/Sighting/129124082</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129124084</v>
+        <v>129124083</v>
       </c>
       <c r="B176" t="n">
         <v>79917</v>
@@ -20408,10 +20409,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>421591</v>
+        <v>421598</v>
       </c>
       <c r="R176" t="n">
-        <v>6787819</v>
+        <v>6787829</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20443,7 +20444,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -20453,7 +20454,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20479,13 +20480,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124084</t>
+          <t>https://artportalen.se/Sighting/129124083</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129124085</v>
+        <v>129124084</v>
       </c>
       <c r="B177" t="n">
         <v>79917</v>
@@ -20520,10 +20521,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>421622</v>
+        <v>421591</v>
       </c>
       <c r="R177" t="n">
-        <v>6787726</v>
+        <v>6787819</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20555,7 +20556,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -20565,7 +20566,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20591,16 +20592,16 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124085</t>
+          <t>https://artportalen.se/Sighting/129124084</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129124091</v>
+        <v>129124085</v>
       </c>
       <c r="B178" t="n">
-        <v>79350</v>
+        <v>79917</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20608,21 +20609,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -20632,10 +20633,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>421255</v>
+        <v>421622</v>
       </c>
       <c r="R178" t="n">
-        <v>6788442</v>
+        <v>6787726</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20667,7 +20668,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -20677,7 +20678,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20703,16 +20704,16 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124091</t>
+          <t>https://artportalen.se/Sighting/129124085</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>137209425</v>
+        <v>129124091</v>
       </c>
       <c r="B179" t="n">
-        <v>79539</v>
+        <v>79350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20744,13 +20745,13 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>421202</v>
+        <v>421255</v>
       </c>
       <c r="R179" t="n">
-        <v>6788653</v>
+        <v>6788442</v>
       </c>
       <c r="S179" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -20774,22 +20775,22 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20804,18 +20805,242 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/129124091</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>137209425</v>
+      </c>
+      <c r="B180" t="n">
+        <v>79544</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Blåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>421202</v>
+      </c>
+      <c r="R180" t="n">
+        <v>6788653</v>
+      </c>
+      <c r="S180" t="n">
+        <v>9</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137209425</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>137403524</v>
+      </c>
+      <c r="B181" t="n">
+        <v>79544</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Blåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>421163</v>
+      </c>
+      <c r="R181" t="n">
+        <v>6788627</v>
+      </c>
+      <c r="S181" t="n">
+        <v>7</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist, Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137403524</t>
         </is>
       </c>
     </row>
@@ -20999,6 +21224,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -8551,7 +8551,7 @@
         <v>137237604</v>
       </c>
       <c r="B72" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>137209425</v>
       </c>
       <c r="B180" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>137403524</v>
       </c>
       <c r="B181" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -8551,7 +8551,7 @@
         <v>137237604</v>
       </c>
       <c r="B72" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>137209425</v>
       </c>
       <c r="B180" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>137403524</v>
       </c>
       <c r="B181" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -8551,7 +8551,7 @@
         <v>137237604</v>
       </c>
       <c r="B72" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>137209425</v>
       </c>
       <c r="B180" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>137403524</v>
       </c>
       <c r="B181" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>

--- a/artfynd/A 46800-2025 artfynd.xlsx
+++ b/artfynd/A 46800-2025 artfynd.xlsx
@@ -680,45 +680,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129124183</v>
+        <v>88280081</v>
       </c>
       <c r="B2" t="n">
-        <v>78993</v>
+        <v>12703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
+        <v>105850</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Corticeus longulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Gyllenhal, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>sållning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Hädbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421744</v>
+        <v>421414</v>
       </c>
       <c r="R2" t="n">
-        <v>6788480</v>
+        <v>6788091</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +754,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:40</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:40</t>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ett dött ex (torrt fragment) utanpå bark. Övriga arter: timmerman (kläckhål), barrträdlöpare och allmän barkplattbagge (larver), Phloenomus, troligen lapponica, Phloeopora testacea, Placusa, troligen depressa (många ex)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,66 +775,90 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Gles tallskog på svag sydvästsluttning, delvis försumpad</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Nydöd tall 37 cm, gröna, gula, bruna och röda barr, med båda arter märgborrar</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Lars-Ove Wikars</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Lars-Ove Wikars, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Insekter på tallved i Dalarna 2020 - 2021</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124183</t>
+          <t>https://artportalen.se/Sighting/88280081</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129124184</v>
+        <v>88280082</v>
       </c>
       <c r="B3" t="n">
-        <v>78993</v>
+        <v>8455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Hädbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421751</v>
+        <v>421414</v>
       </c>
       <c r="R3" t="n">
-        <v>6788483</v>
+        <v>6788091</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +885,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gnagspår och fragment, tillsammans med större märgborre. Den mindre föredrar tydligt sydsidan, här ned till 120 cm från rot</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,31 +906,45 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Gles tallskog på svag sydvästsluttning, delvis försumpad</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Nydöd tall 37 cm, gröna, gula, bruna och röda barr</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Lars-Ove Wikars, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Insekter på tallved i Dalarna 2020 - 2021</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124184</t>
+          <t>https://artportalen.se/Sighting/88280082</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129124185</v>
+        <v>129124102</v>
       </c>
       <c r="B4" t="n">
-        <v>78993</v>
+        <v>83302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +952,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +976,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421684</v>
+        <v>421694</v>
       </c>
       <c r="R4" t="n">
-        <v>6788390</v>
+        <v>6787682</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +1011,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,14 +1021,14 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1010,16 +1047,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124185</t>
+          <t>https://artportalen.se/Sighting/129124102</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129124171</v>
+        <v>129124174</v>
       </c>
       <c r="B5" t="n">
-        <v>93197</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1064,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421673</v>
+        <v>421411</v>
       </c>
       <c r="R5" t="n">
-        <v>6788450</v>
+        <v>6788357</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1123,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1133,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,38 +1159,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124171</t>
+          <t>https://artportalen.se/Sighting/129124174</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129124161</v>
+        <v>129124175</v>
       </c>
       <c r="B6" t="n">
-        <v>79327</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>421701</v>
+        <v>421343</v>
       </c>
       <c r="R6" t="n">
-        <v>6788470</v>
+        <v>6788400</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,38 +1271,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124161</t>
+          <t>https://artportalen.se/Sighting/129124175</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129124162</v>
+        <v>129124176</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421720</v>
+        <v>421338</v>
       </c>
       <c r="R7" t="n">
-        <v>6788450</v>
+        <v>6788476</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1357,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,16 +1383,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124162</t>
+          <t>https://artportalen.se/Sighting/129124176</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129124066</v>
+        <v>129124177</v>
       </c>
       <c r="B8" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1400,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1424,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>421685</v>
+        <v>421318</v>
       </c>
       <c r="R8" t="n">
-        <v>6788462</v>
+        <v>6788511</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1469,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,16 +1495,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124066</t>
+          <t>https://artportalen.se/Sighting/129124177</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129124067</v>
+        <v>129124178</v>
       </c>
       <c r="B9" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,21 +1512,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1536,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421751</v>
+        <v>421235</v>
       </c>
       <c r="R9" t="n">
-        <v>6788483</v>
+        <v>6788559</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1571,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1581,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,56 +1607,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124067</t>
+          <t>https://artportalen.se/Sighting/129124178</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129124118</v>
+        <v>129124179</v>
       </c>
       <c r="B10" t="n">
-        <v>8455</v>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421732</v>
+        <v>421487</v>
       </c>
       <c r="R10" t="n">
-        <v>6788486</v>
+        <v>6788638</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1683,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1693,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,16 +1719,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124118</t>
+          <t>https://artportalen.se/Sighting/129124179</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129124092</v>
+        <v>129124180</v>
       </c>
       <c r="B11" t="n">
-        <v>79350</v>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,21 +1736,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>260591</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>421696</v>
+        <v>421501</v>
       </c>
       <c r="R11" t="n">
-        <v>6788469</v>
+        <v>6788671</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1805,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,16 +1831,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124092</t>
+          <t>https://artportalen.se/Sighting/129124180</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129124102</v>
+        <v>129124181</v>
       </c>
       <c r="B12" t="n">
-        <v>83302</v>
+        <v>78993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,21 +1848,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>310</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1872,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>421694</v>
+        <v>421537</v>
       </c>
       <c r="R12" t="n">
-        <v>6787682</v>
+        <v>6788706</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1907,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,14 +1917,14 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>
@@ -1911,13 +1943,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124102</t>
+          <t>https://artportalen.se/Sighting/129124181</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129124174</v>
+        <v>129124182</v>
       </c>
       <c r="B13" t="n">
         <v>78993</v>
@@ -1952,10 +1984,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>421411</v>
+        <v>421622</v>
       </c>
       <c r="R13" t="n">
-        <v>6788357</v>
+        <v>6788520</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +2029,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,13 +2055,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124174</t>
+          <t>https://artportalen.se/Sighting/129124182</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129124175</v>
+        <v>129124183</v>
       </c>
       <c r="B14" t="n">
         <v>78993</v>
@@ -2064,10 +2096,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421343</v>
+        <v>421744</v>
       </c>
       <c r="R14" t="n">
-        <v>6788400</v>
+        <v>6788480</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,13 +2167,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124175</t>
+          <t>https://artportalen.se/Sighting/129124183</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129124176</v>
+        <v>129124184</v>
       </c>
       <c r="B15" t="n">
         <v>78993</v>
@@ -2176,10 +2208,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421338</v>
+        <v>421751</v>
       </c>
       <c r="R15" t="n">
-        <v>6788476</v>
+        <v>6788483</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,13 +2279,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124176</t>
+          <t>https://artportalen.se/Sighting/129124184</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129124177</v>
+        <v>129124185</v>
       </c>
       <c r="B16" t="n">
         <v>78993</v>
@@ -2288,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421318</v>
+        <v>421684</v>
       </c>
       <c r="R16" t="n">
-        <v>6788511</v>
+        <v>6788390</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2323,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,13 +2391,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124177</t>
+          <t>https://artportalen.se/Sighting/129124185</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129124178</v>
+        <v>129124186</v>
       </c>
       <c r="B17" t="n">
         <v>78993</v>
@@ -2400,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421235</v>
+        <v>421626</v>
       </c>
       <c r="R17" t="n">
-        <v>6788559</v>
+        <v>6787877</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2435,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,7 +2477,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,16 +2503,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124178</t>
+          <t>https://artportalen.se/Sighting/129124186</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129124179</v>
+        <v>129124087</v>
       </c>
       <c r="B18" t="n">
-        <v>78993</v>
+        <v>79422</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2488,21 +2520,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>967</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2544,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421487</v>
+        <v>421601</v>
       </c>
       <c r="R18" t="n">
-        <v>6788638</v>
+        <v>6787830</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2547,7 +2579,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2589,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,38 +2615,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124179</t>
+          <t>https://artportalen.se/Sighting/129124087</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129124180</v>
+        <v>129124146</v>
       </c>
       <c r="B19" t="n">
-        <v>78993</v>
+        <v>92083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,10 +2656,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421501</v>
+        <v>421654</v>
       </c>
       <c r="R19" t="n">
-        <v>6788671</v>
+        <v>6788448</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,7 +2691,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2701,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,16 +2727,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124180</t>
+          <t>https://artportalen.se/Sighting/129124146</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129124181</v>
+        <v>129124171</v>
       </c>
       <c r="B20" t="n">
-        <v>78993</v>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,21 +2744,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2736,10 +2768,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421537</v>
+        <v>421673</v>
       </c>
       <c r="R20" t="n">
-        <v>6788706</v>
+        <v>6788450</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2771,7 +2803,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2781,7 +2813,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2807,16 +2839,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124181</t>
+          <t>https://artportalen.se/Sighting/129124171</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129124182</v>
+        <v>129124172</v>
       </c>
       <c r="B21" t="n">
-        <v>78993</v>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,21 +2856,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2848,10 +2880,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421622</v>
+        <v>421420</v>
       </c>
       <c r="R21" t="n">
-        <v>6788520</v>
+        <v>6788401</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2883,7 +2915,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,7 +2925,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,16 +2951,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124182</t>
+          <t>https://artportalen.se/Sighting/129124172</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129124186</v>
+        <v>129124173</v>
       </c>
       <c r="B22" t="n">
-        <v>78993</v>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2936,21 +2968,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2960,10 +2992,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421626</v>
+        <v>421621</v>
       </c>
       <c r="R22" t="n">
-        <v>6787877</v>
+        <v>6787838</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2995,7 +3027,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3005,7 +3037,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,16 +3063,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124186</t>
+          <t>https://artportalen.se/Sighting/129124173</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129124087</v>
+        <v>129124090</v>
       </c>
       <c r="B23" t="n">
-        <v>79422</v>
+        <v>91930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3048,21 +3080,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>967</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3072,10 +3104,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421601</v>
+        <v>421576</v>
       </c>
       <c r="R23" t="n">
-        <v>6787830</v>
+        <v>6788373</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3107,7 +3139,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3117,7 +3149,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ej märkt med hänsyn</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3143,51 +3180,60 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124087</t>
+          <t>https://artportalen.se/Sighting/129124090</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129124146</v>
+        <v>129124104</v>
       </c>
       <c r="B24" t="n">
-        <v>92083</v>
+        <v>93235</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421654</v>
+        <v>421407</v>
       </c>
       <c r="R24" t="n">
-        <v>6788448</v>
+        <v>6788349</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3219,7 +3265,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3229,7 +3275,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3255,16 +3301,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124146</t>
+          <t>https://artportalen.se/Sighting/129124104</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129124172</v>
+        <v>129124105</v>
       </c>
       <c r="B25" t="n">
-        <v>93197</v>
+        <v>93235</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,34 +3318,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421420</v>
+        <v>421613</v>
       </c>
       <c r="R25" t="n">
-        <v>6788401</v>
+        <v>6788634</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3331,7 +3386,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3341,7 +3396,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3367,51 +3422,51 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124172</t>
+          <t>https://artportalen.se/Sighting/129124105</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129124173</v>
+        <v>129093008</v>
       </c>
       <c r="B26" t="n">
-        <v>93197</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421621</v>
+        <v>421318</v>
       </c>
       <c r="R26" t="n">
-        <v>6787838</v>
+        <v>6788252</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3443,7 +3498,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3453,7 +3508,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3468,62 +3523,62 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124173</t>
+          <t>https://artportalen.se/Sighting/129093008</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129124090</v>
+        <v>129093018</v>
       </c>
       <c r="B27" t="n">
-        <v>91930</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>421576</v>
+        <v>421341</v>
       </c>
       <c r="R27" t="n">
-        <v>6788373</v>
+        <v>6788261</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3555,7 +3610,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3565,12 +3620,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ej märkt med hänsyn</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3585,71 +3635,62 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124090</t>
+          <t>https://artportalen.se/Sighting/129093018</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129124104</v>
+        <v>129093043</v>
       </c>
       <c r="B28" t="n">
-        <v>93235</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>421407</v>
+        <v>421355</v>
       </c>
       <c r="R28" t="n">
-        <v>6788349</v>
+        <v>6788265</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3681,7 +3722,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3691,7 +3732,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3706,71 +3747,62 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124104</t>
+          <t>https://artportalen.se/Sighting/129093043</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129124105</v>
+        <v>129093167</v>
       </c>
       <c r="B29" t="n">
-        <v>93235</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421613</v>
+        <v>421391</v>
       </c>
       <c r="R29" t="n">
-        <v>6788634</v>
+        <v>6788314</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3802,7 +3834,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3812,7 +3844,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3827,24 +3859,24 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124105</t>
+          <t>https://artportalen.se/Sighting/129093167</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129093008</v>
+        <v>129093173</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -3879,10 +3911,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>421318</v>
+        <v>421390</v>
       </c>
       <c r="R30" t="n">
-        <v>6788252</v>
+        <v>6788380</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3950,13 +3982,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093008</t>
+          <t>https://artportalen.se/Sighting/129093173</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129093018</v>
+        <v>129093174</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -3991,10 +4023,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>421341</v>
+        <v>421394</v>
       </c>
       <c r="R31" t="n">
-        <v>6788261</v>
+        <v>6788396</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4062,13 +4094,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093018</t>
+          <t>https://artportalen.se/Sighting/129093174</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129093043</v>
+        <v>129093188</v>
       </c>
       <c r="B32" t="n">
         <v>79327</v>
@@ -4103,10 +4135,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>421355</v>
+        <v>421407</v>
       </c>
       <c r="R32" t="n">
-        <v>6788265</v>
+        <v>6788409</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4174,13 +4206,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093043</t>
+          <t>https://artportalen.se/Sighting/129093188</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129093167</v>
+        <v>129093226</v>
       </c>
       <c r="B33" t="n">
         <v>79327</v>
@@ -4215,10 +4247,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>421391</v>
+        <v>421395</v>
       </c>
       <c r="R33" t="n">
-        <v>6788314</v>
+        <v>6788438</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4286,13 +4318,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093167</t>
+          <t>https://artportalen.se/Sighting/129093226</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129093173</v>
+        <v>129093929</v>
       </c>
       <c r="B34" t="n">
         <v>79327</v>
@@ -4327,10 +4359,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>421390</v>
+        <v>421399</v>
       </c>
       <c r="R34" t="n">
-        <v>6788380</v>
+        <v>6788487</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4398,13 +4430,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093173</t>
+          <t>https://artportalen.se/Sighting/129093929</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129093174</v>
+        <v>129093983</v>
       </c>
       <c r="B35" t="n">
         <v>79327</v>
@@ -4439,10 +4471,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>421394</v>
+        <v>421400</v>
       </c>
       <c r="R35" t="n">
-        <v>6788396</v>
+        <v>6788524</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4510,13 +4542,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093174</t>
+          <t>https://artportalen.se/Sighting/129093983</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129093188</v>
+        <v>129094012</v>
       </c>
       <c r="B36" t="n">
         <v>79327</v>
@@ -4551,10 +4583,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>421407</v>
+        <v>421379</v>
       </c>
       <c r="R36" t="n">
-        <v>6788409</v>
+        <v>6788540</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4622,13 +4654,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093188</t>
+          <t>https://artportalen.se/Sighting/129094012</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129093226</v>
+        <v>129094091</v>
       </c>
       <c r="B37" t="n">
         <v>79327</v>
@@ -4663,10 +4695,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>421395</v>
+        <v>421397</v>
       </c>
       <c r="R37" t="n">
-        <v>6788438</v>
+        <v>6788565</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4734,13 +4766,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093226</t>
+          <t>https://artportalen.se/Sighting/129094091</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129093929</v>
+        <v>129094103</v>
       </c>
       <c r="B38" t="n">
         <v>79327</v>
@@ -4775,10 +4807,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>421399</v>
+        <v>421421</v>
       </c>
       <c r="R38" t="n">
-        <v>6788487</v>
+        <v>6788547</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4846,13 +4878,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093929</t>
+          <t>https://artportalen.se/Sighting/129094103</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129093983</v>
+        <v>129094170</v>
       </c>
       <c r="B39" t="n">
         <v>79327</v>
@@ -4887,10 +4919,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>421400</v>
+        <v>421499</v>
       </c>
       <c r="R39" t="n">
-        <v>6788524</v>
+        <v>6788592</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4958,13 +4990,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093983</t>
+          <t>https://artportalen.se/Sighting/129094170</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129094012</v>
+        <v>129094179</v>
       </c>
       <c r="B40" t="n">
         <v>79327</v>
@@ -4999,10 +5031,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>421379</v>
+        <v>421509</v>
       </c>
       <c r="R40" t="n">
-        <v>6788540</v>
+        <v>6788597</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5070,13 +5102,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094012</t>
+          <t>https://artportalen.se/Sighting/129094179</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129094091</v>
+        <v>129094800</v>
       </c>
       <c r="B41" t="n">
         <v>79327</v>
@@ -5111,10 +5143,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>421397</v>
+        <v>421501</v>
       </c>
       <c r="R41" t="n">
-        <v>6788565</v>
+        <v>6788477</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5182,13 +5214,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094091</t>
+          <t>https://artportalen.se/Sighting/129094800</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129094103</v>
+        <v>129095256</v>
       </c>
       <c r="B42" t="n">
         <v>79327</v>
@@ -5223,10 +5255,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>421421</v>
+        <v>421440</v>
       </c>
       <c r="R42" t="n">
-        <v>6788547</v>
+        <v>6788407</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5294,13 +5326,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094103</t>
+          <t>https://artportalen.se/Sighting/129095256</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129094170</v>
+        <v>129095317</v>
       </c>
       <c r="B43" t="n">
         <v>79327</v>
@@ -5335,10 +5367,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>421499</v>
+        <v>421398</v>
       </c>
       <c r="R43" t="n">
-        <v>6788592</v>
+        <v>6788372</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5406,13 +5438,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094170</t>
+          <t>https://artportalen.se/Sighting/129095317</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129094179</v>
+        <v>129095392</v>
       </c>
       <c r="B44" t="n">
         <v>79327</v>
@@ -5447,10 +5479,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>421509</v>
+        <v>421342</v>
       </c>
       <c r="R44" t="n">
-        <v>6788597</v>
+        <v>6788310</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5518,13 +5550,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094179</t>
+          <t>https://artportalen.se/Sighting/129095392</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129094800</v>
+        <v>129096050</v>
       </c>
       <c r="B45" t="n">
         <v>79327</v>
@@ -5559,10 +5591,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>421501</v>
+        <v>421635</v>
       </c>
       <c r="R45" t="n">
-        <v>6788477</v>
+        <v>6787819</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5630,13 +5662,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094800</t>
+          <t>https://artportalen.se/Sighting/129096050</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129095256</v>
+        <v>129124147</v>
       </c>
       <c r="B46" t="n">
         <v>79327</v>
@@ -5667,14 +5699,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>421440</v>
+        <v>421437</v>
       </c>
       <c r="R46" t="n">
-        <v>6788407</v>
+        <v>6788275</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5706,7 +5738,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5716,7 +5748,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5731,24 +5763,24 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095256</t>
+          <t>https://artportalen.se/Sighting/129124147</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129095317</v>
+        <v>129124148</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5779,14 +5811,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>421398</v>
+        <v>421395</v>
       </c>
       <c r="R47" t="n">
-        <v>6788372</v>
+        <v>6788374</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5818,7 +5850,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5828,7 +5860,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5843,24 +5875,24 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095317</t>
+          <t>https://artportalen.se/Sighting/129124148</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129095392</v>
+        <v>129124149</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -5891,14 +5923,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>421342</v>
+        <v>421376</v>
       </c>
       <c r="R48" t="n">
-        <v>6788310</v>
+        <v>6788380</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5930,7 +5962,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5940,7 +5972,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5955,24 +5987,24 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095392</t>
+          <t>https://artportalen.se/Sighting/129124149</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129096050</v>
+        <v>129124150</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -6003,14 +6035,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>421635</v>
+        <v>421349</v>
       </c>
       <c r="R49" t="n">
-        <v>6787819</v>
+        <v>6788397</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6042,7 +6074,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6052,7 +6084,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6067,24 +6099,24 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129096050</t>
+          <t>https://artportalen.se/Sighting/129124150</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129124147</v>
+        <v>129124151</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -6119,10 +6151,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>421437</v>
+        <v>421275</v>
       </c>
       <c r="R50" t="n">
-        <v>6788275</v>
+        <v>6788430</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6154,7 +6186,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6164,7 +6196,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6190,13 +6222,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124147</t>
+          <t>https://artportalen.se/Sighting/129124151</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129124148</v>
+        <v>129124152</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -6231,10 +6263,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>421395</v>
+        <v>421234</v>
       </c>
       <c r="R51" t="n">
-        <v>6788374</v>
+        <v>6788411</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6266,7 +6298,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6276,7 +6308,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6302,13 +6334,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124148</t>
+          <t>https://artportalen.se/Sighting/129124152</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129124149</v>
+        <v>129124153</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -6343,10 +6375,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>421376</v>
+        <v>421305</v>
       </c>
       <c r="R52" t="n">
-        <v>6788380</v>
+        <v>6788474</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6378,7 +6410,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6388,7 +6420,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6414,13 +6446,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124149</t>
+          <t>https://artportalen.se/Sighting/129124153</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129124150</v>
+        <v>129124154</v>
       </c>
       <c r="B53" t="n">
         <v>79327</v>
@@ -6455,10 +6487,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>421349</v>
+        <v>421303</v>
       </c>
       <c r="R53" t="n">
-        <v>6788397</v>
+        <v>6788456</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6490,7 +6522,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6500,7 +6532,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6526,13 +6558,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124150</t>
+          <t>https://artportalen.se/Sighting/129124154</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129124151</v>
+        <v>129124155</v>
       </c>
       <c r="B54" t="n">
         <v>79327</v>
@@ -6567,10 +6599,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>421275</v>
+        <v>421354</v>
       </c>
       <c r="R54" t="n">
-        <v>6788430</v>
+        <v>6788463</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6602,7 +6634,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6612,7 +6644,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6638,13 +6670,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124151</t>
+          <t>https://artportalen.se/Sighting/129124155</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129124152</v>
+        <v>129124156</v>
       </c>
       <c r="B55" t="n">
         <v>79327</v>
@@ -6679,10 +6711,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>421234</v>
+        <v>421351</v>
       </c>
       <c r="R55" t="n">
-        <v>6788411</v>
+        <v>6788471</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6714,7 +6746,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6724,7 +6756,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6750,13 +6782,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124152</t>
+          <t>https://artportalen.se/Sighting/129124156</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129124153</v>
+        <v>129124157</v>
       </c>
       <c r="B56" t="n">
         <v>79327</v>
@@ -6791,10 +6823,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>421305</v>
+        <v>421271</v>
       </c>
       <c r="R56" t="n">
-        <v>6788474</v>
+        <v>6788641</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6826,7 +6858,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6836,7 +6868,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6862,13 +6894,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124153</t>
+          <t>https://artportalen.se/Sighting/129124157</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129124154</v>
+        <v>129124158</v>
       </c>
       <c r="B57" t="n">
         <v>79327</v>
@@ -6903,10 +6935,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>421303</v>
+        <v>421383</v>
       </c>
       <c r="R57" t="n">
-        <v>6788456</v>
+        <v>6788546</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6938,7 +6970,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6948,7 +6980,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6974,13 +7006,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124154</t>
+          <t>https://artportalen.se/Sighting/129124158</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129124155</v>
+        <v>129124159</v>
       </c>
       <c r="B58" t="n">
         <v>79327</v>
@@ -7015,10 +7047,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>421354</v>
+        <v>421612</v>
       </c>
       <c r="R58" t="n">
-        <v>6788463</v>
+        <v>6788488</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7050,7 +7082,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7060,7 +7092,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7086,13 +7118,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124155</t>
+          <t>https://artportalen.se/Sighting/129124159</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129124156</v>
+        <v>129124160</v>
       </c>
       <c r="B59" t="n">
         <v>79327</v>
@@ -7127,10 +7159,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>421351</v>
+        <v>421611</v>
       </c>
       <c r="R59" t="n">
-        <v>6788471</v>
+        <v>6788481</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7162,7 +7194,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7172,7 +7204,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7198,13 +7230,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124156</t>
+          <t>https://artportalen.se/Sighting/129124160</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129124157</v>
+        <v>129124161</v>
       </c>
       <c r="B60" t="n">
         <v>79327</v>
@@ -7239,10 +7271,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>421271</v>
+        <v>421701</v>
       </c>
       <c r="R60" t="n">
-        <v>6788641</v>
+        <v>6788470</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7274,7 +7306,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7284,7 +7316,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7310,13 +7342,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124157</t>
+          <t>https://artportalen.se/Sighting/129124161</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129124158</v>
+        <v>129124162</v>
       </c>
       <c r="B61" t="n">
         <v>79327</v>
@@ -7351,10 +7383,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>421383</v>
+        <v>421720</v>
       </c>
       <c r="R61" t="n">
-        <v>6788546</v>
+        <v>6788450</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7386,7 +7418,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7396,7 +7428,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7422,13 +7454,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124158</t>
+          <t>https://artportalen.se/Sighting/129124162</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129124159</v>
+        <v>129124163</v>
       </c>
       <c r="B62" t="n">
         <v>79327</v>
@@ -7463,10 +7495,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>421612</v>
+        <v>421454</v>
       </c>
       <c r="R62" t="n">
-        <v>6788488</v>
+        <v>6788422</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7498,7 +7530,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7508,7 +7540,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7534,13 +7566,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124159</t>
+          <t>https://artportalen.se/Sighting/129124163</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129124160</v>
+        <v>129124164</v>
       </c>
       <c r="B63" t="n">
         <v>79327</v>
@@ -7575,10 +7607,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>421611</v>
+        <v>421345</v>
       </c>
       <c r="R63" t="n">
-        <v>6788481</v>
+        <v>6788394</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7610,7 +7642,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7620,7 +7652,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7646,13 +7678,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124160</t>
+          <t>https://artportalen.se/Sighting/129124164</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129124163</v>
+        <v>129124165</v>
       </c>
       <c r="B64" t="n">
         <v>79327</v>
@@ -7687,10 +7719,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>421454</v>
+        <v>421340</v>
       </c>
       <c r="R64" t="n">
-        <v>6788422</v>
+        <v>6788389</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7722,7 +7754,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7732,7 +7764,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7758,13 +7790,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124163</t>
+          <t>https://artportalen.se/Sighting/129124165</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129124164</v>
+        <v>129124166</v>
       </c>
       <c r="B65" t="n">
         <v>79327</v>
@@ -7799,10 +7831,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>421345</v>
+        <v>421316</v>
       </c>
       <c r="R65" t="n">
-        <v>6788394</v>
+        <v>6788317</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7834,7 +7866,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7844,7 +7876,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7870,13 +7902,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124164</t>
+          <t>https://artportalen.se/Sighting/129124166</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129124165</v>
+        <v>129124167</v>
       </c>
       <c r="B66" t="n">
         <v>79327</v>
@@ -7911,10 +7943,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>421340</v>
+        <v>421342</v>
       </c>
       <c r="R66" t="n">
-        <v>6788389</v>
+        <v>6788261</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7946,7 +7978,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7956,7 +7988,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7982,13 +8014,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124165</t>
+          <t>https://artportalen.se/Sighting/129124167</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129124166</v>
+        <v>129124168</v>
       </c>
       <c r="B67" t="n">
         <v>79327</v>
@@ -8023,10 +8055,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>421316</v>
+        <v>421329</v>
       </c>
       <c r="R67" t="n">
-        <v>6788317</v>
+        <v>6788222</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8058,7 +8090,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8068,7 +8100,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8094,13 +8126,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124166</t>
+          <t>https://artportalen.se/Sighting/129124168</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129124167</v>
+        <v>129124169</v>
       </c>
       <c r="B68" t="n">
         <v>79327</v>
@@ -8135,10 +8167,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>421342</v>
+        <v>421618</v>
       </c>
       <c r="R68" t="n">
-        <v>6788261</v>
+        <v>6787872</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8170,7 +8202,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8180,7 +8212,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8206,13 +8238,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124167</t>
+          <t>https://artportalen.se/Sighting/129124169</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129124168</v>
+        <v>129124170</v>
       </c>
       <c r="B69" t="n">
         <v>79327</v>
@@ -8247,10 +8279,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>421329</v>
+        <v>421604</v>
       </c>
       <c r="R69" t="n">
-        <v>6788222</v>
+        <v>6787823</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8282,7 +8314,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8292,7 +8324,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8318,16 +8350,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124168</t>
+          <t>https://artportalen.se/Sighting/129124170</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129124169</v>
+        <v>137237604</v>
       </c>
       <c r="B70" t="n">
-        <v>79327</v>
+        <v>79539</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8359,13 +8391,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>421618</v>
+        <v>421176</v>
       </c>
       <c r="R70" t="n">
-        <v>6787872</v>
+        <v>6788647</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8389,22 +8421,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8419,49 +8451,49 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124169</t>
+          <t>https://artportalen.se/Sighting/137237604</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129124170</v>
+        <v>129124187</v>
       </c>
       <c r="B71" t="n">
-        <v>79327</v>
+        <v>78730</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8471,10 +8503,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>421604</v>
+        <v>421639</v>
       </c>
       <c r="R71" t="n">
-        <v>6787823</v>
+        <v>6788393</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8506,7 +8538,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8516,7 +8548,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8542,54 +8574,54 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124170</t>
+          <t>https://artportalen.se/Sighting/129124187</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>137237604</v>
+        <v>129095733</v>
       </c>
       <c r="B72" t="n">
-        <v>79535</v>
+        <v>79084</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>421176</v>
+        <v>421655</v>
       </c>
       <c r="R72" t="n">
-        <v>6788647</v>
+        <v>6787687</v>
       </c>
       <c r="S72" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8613,22 +8645,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8643,27 +8675,27 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237604</t>
+          <t>https://artportalen.se/Sighting/129095733</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129124187</v>
+        <v>129124137</v>
       </c>
       <c r="B73" t="n">
-        <v>78730</v>
+        <v>79084</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8671,21 +8703,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8695,7 +8727,7 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>421639</v>
+        <v>421312</v>
       </c>
       <c r="R73" t="n">
         <v>6788393</v>
@@ -8730,7 +8762,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8740,7 +8772,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8766,13 +8798,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124187</t>
+          <t>https://artportalen.se/Sighting/129124137</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129095733</v>
+        <v>129124138</v>
       </c>
       <c r="B74" t="n">
         <v>79084</v>
@@ -8803,14 +8835,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>421655</v>
+        <v>421292</v>
       </c>
       <c r="R74" t="n">
-        <v>6787687</v>
+        <v>6788456</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8842,7 +8874,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8852,7 +8884,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8867,24 +8899,24 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095733</t>
+          <t>https://artportalen.se/Sighting/129124138</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129124137</v>
+        <v>129124139</v>
       </c>
       <c r="B75" t="n">
         <v>79084</v>
@@ -8919,10 +8951,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>421312</v>
+        <v>421354</v>
       </c>
       <c r="R75" t="n">
-        <v>6788393</v>
+        <v>6788463</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8954,7 +8986,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8964,7 +8996,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8990,13 +9022,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124137</t>
+          <t>https://artportalen.se/Sighting/129124139</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129124138</v>
+        <v>129124140</v>
       </c>
       <c r="B76" t="n">
         <v>79084</v>
@@ -9031,10 +9063,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>421292</v>
+        <v>421656</v>
       </c>
       <c r="R76" t="n">
-        <v>6788456</v>
+        <v>6787791</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9066,7 +9098,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9076,7 +9108,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9102,13 +9134,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124138</t>
+          <t>https://artportalen.se/Sighting/129124140</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129124139</v>
+        <v>129124141</v>
       </c>
       <c r="B77" t="n">
         <v>79084</v>
@@ -9143,10 +9175,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>421354</v>
+        <v>421616</v>
       </c>
       <c r="R77" t="n">
-        <v>6788463</v>
+        <v>6787883</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9178,7 +9210,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9188,7 +9220,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9214,13 +9246,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124139</t>
+          <t>https://artportalen.se/Sighting/129124141</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129124140</v>
+        <v>129124142</v>
       </c>
       <c r="B78" t="n">
         <v>79084</v>
@@ -9255,10 +9287,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>421656</v>
+        <v>421594</v>
       </c>
       <c r="R78" t="n">
-        <v>6787791</v>
+        <v>6787870</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9290,7 +9322,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9300,7 +9332,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9326,13 +9358,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124140</t>
+          <t>https://artportalen.se/Sighting/129124142</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129124141</v>
+        <v>129124143</v>
       </c>
       <c r="B79" t="n">
         <v>79084</v>
@@ -9367,10 +9399,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>421616</v>
+        <v>421596</v>
       </c>
       <c r="R79" t="n">
-        <v>6787883</v>
+        <v>6787835</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9402,7 +9434,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9412,7 +9444,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9438,13 +9470,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124141</t>
+          <t>https://artportalen.se/Sighting/129124143</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129124142</v>
+        <v>129124144</v>
       </c>
       <c r="B80" t="n">
         <v>79084</v>
@@ -9479,10 +9511,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>421594</v>
+        <v>421602</v>
       </c>
       <c r="R80" t="n">
-        <v>6787870</v>
+        <v>6787829</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9514,7 +9546,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9524,7 +9556,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9550,13 +9582,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124142</t>
+          <t>https://artportalen.se/Sighting/129124144</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129124143</v>
+        <v>129124145</v>
       </c>
       <c r="B81" t="n">
         <v>79084</v>
@@ -9591,10 +9623,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>421596</v>
+        <v>421591</v>
       </c>
       <c r="R81" t="n">
-        <v>6787835</v>
+        <v>6787819</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9626,7 +9658,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9636,7 +9668,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9662,16 +9694,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124143</t>
+          <t>https://artportalen.se/Sighting/129124145</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129124144</v>
+        <v>129093027</v>
       </c>
       <c r="B82" t="n">
-        <v>79084</v>
+        <v>79946</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9679,34 +9711,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>421602</v>
+        <v>421341</v>
       </c>
       <c r="R82" t="n">
-        <v>6787829</v>
+        <v>6788261</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9738,7 +9770,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9748,7 +9780,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9763,27 +9795,27 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124144</t>
+          <t>https://artportalen.se/Sighting/129093027</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129124145</v>
+        <v>129093086</v>
       </c>
       <c r="B83" t="n">
-        <v>79084</v>
+        <v>79946</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9791,34 +9823,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>421591</v>
+        <v>421380</v>
       </c>
       <c r="R83" t="n">
-        <v>6787819</v>
+        <v>6788287</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9850,7 +9882,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9860,7 +9892,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9875,24 +9907,24 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124145</t>
+          <t>https://artportalen.se/Sighting/129093086</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129093027</v>
+        <v>129093766</v>
       </c>
       <c r="B84" t="n">
         <v>79946</v>
@@ -9927,10 +9959,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>421341</v>
+        <v>421371</v>
       </c>
       <c r="R84" t="n">
-        <v>6788261</v>
+        <v>6788472</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9998,13 +10030,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093027</t>
+          <t>https://artportalen.se/Sighting/129093766</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129093086</v>
+        <v>129094072</v>
       </c>
       <c r="B85" t="n">
         <v>79946</v>
@@ -10039,10 +10071,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>421380</v>
+        <v>421379</v>
       </c>
       <c r="R85" t="n">
-        <v>6788287</v>
+        <v>6788540</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10110,13 +10142,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093086</t>
+          <t>https://artportalen.se/Sighting/129094072</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129093766</v>
+        <v>129094551</v>
       </c>
       <c r="B86" t="n">
         <v>79946</v>
@@ -10151,10 +10183,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>421371</v>
+        <v>421564</v>
       </c>
       <c r="R86" t="n">
-        <v>6788472</v>
+        <v>6788544</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10222,13 +10254,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093766</t>
+          <t>https://artportalen.se/Sighting/129094551</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129094072</v>
+        <v>129095002</v>
       </c>
       <c r="B87" t="n">
         <v>79946</v>
@@ -10263,10 +10295,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>421379</v>
+        <v>421507</v>
       </c>
       <c r="R87" t="n">
-        <v>6788540</v>
+        <v>6788435</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10334,13 +10366,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094072</t>
+          <t>https://artportalen.se/Sighting/129095002</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129094551</v>
+        <v>129095786</v>
       </c>
       <c r="B88" t="n">
         <v>79946</v>
@@ -10375,10 +10407,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>421564</v>
+        <v>421655</v>
       </c>
       <c r="R88" t="n">
-        <v>6788544</v>
+        <v>6787687</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10446,13 +10478,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094551</t>
+          <t>https://artportalen.se/Sighting/129095786</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129095002</v>
+        <v>129095862</v>
       </c>
       <c r="B89" t="n">
         <v>79946</v>
@@ -10487,10 +10519,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>421507</v>
+        <v>421631</v>
       </c>
       <c r="R89" t="n">
-        <v>6788435</v>
+        <v>6787723</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10558,13 +10590,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095002</t>
+          <t>https://artportalen.se/Sighting/129095862</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129095786</v>
+        <v>129095947</v>
       </c>
       <c r="B90" t="n">
         <v>79946</v>
@@ -10599,10 +10631,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>421655</v>
+        <v>421617</v>
       </c>
       <c r="R90" t="n">
-        <v>6787687</v>
+        <v>6787742</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10670,13 +10702,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095786</t>
+          <t>https://artportalen.se/Sighting/129095947</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129095862</v>
+        <v>129124051</v>
       </c>
       <c r="B91" t="n">
         <v>79946</v>
@@ -10707,14 +10739,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>421631</v>
+        <v>421392</v>
       </c>
       <c r="R91" t="n">
-        <v>6787723</v>
+        <v>6788226</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10746,7 +10778,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10756,7 +10788,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10771,24 +10803,24 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095862</t>
+          <t>https://artportalen.se/Sighting/129124051</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129095947</v>
+        <v>129124052</v>
       </c>
       <c r="B92" t="n">
         <v>79946</v>
@@ -10819,14 +10851,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>421617</v>
+        <v>421391</v>
       </c>
       <c r="R92" t="n">
-        <v>6787742</v>
+        <v>6788209</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10858,7 +10890,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10868,7 +10900,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10883,24 +10915,24 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095947</t>
+          <t>https://artportalen.se/Sighting/129124052</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129124051</v>
+        <v>129124053</v>
       </c>
       <c r="B93" t="n">
         <v>79946</v>
@@ -10935,10 +10967,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>421392</v>
+        <v>421421</v>
       </c>
       <c r="R93" t="n">
-        <v>6788226</v>
+        <v>6788216</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10970,7 +11002,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10980,7 +11012,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11006,13 +11038,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124051</t>
+          <t>https://artportalen.se/Sighting/129124053</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129124052</v>
+        <v>129124054</v>
       </c>
       <c r="B94" t="n">
         <v>79946</v>
@@ -11047,10 +11079,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>421391</v>
+        <v>421423</v>
       </c>
       <c r="R94" t="n">
-        <v>6788209</v>
+        <v>6788261</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11082,7 +11114,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11092,7 +11124,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11118,13 +11150,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124052</t>
+          <t>https://artportalen.se/Sighting/129124054</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129124053</v>
+        <v>129124055</v>
       </c>
       <c r="B95" t="n">
         <v>79946</v>
@@ -11159,10 +11191,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>421421</v>
+        <v>421411</v>
       </c>
       <c r="R95" t="n">
-        <v>6788216</v>
+        <v>6788356</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11194,7 +11226,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11204,7 +11236,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11230,13 +11262,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124053</t>
+          <t>https://artportalen.se/Sighting/129124055</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129124054</v>
+        <v>129124056</v>
       </c>
       <c r="B96" t="n">
         <v>79946</v>
@@ -11271,10 +11303,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>421423</v>
+        <v>421343</v>
       </c>
       <c r="R96" t="n">
-        <v>6788261</v>
+        <v>6788400</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11306,7 +11338,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11316,7 +11348,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11342,13 +11374,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124054</t>
+          <t>https://artportalen.se/Sighting/129124056</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129124055</v>
+        <v>129124057</v>
       </c>
       <c r="B97" t="n">
         <v>79946</v>
@@ -11383,10 +11415,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>421411</v>
+        <v>421312</v>
       </c>
       <c r="R97" t="n">
-        <v>6788356</v>
+        <v>6788393</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11418,7 +11450,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11428,7 +11460,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11454,13 +11486,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124055</t>
+          <t>https://artportalen.se/Sighting/129124057</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129124056</v>
+        <v>129124058</v>
       </c>
       <c r="B98" t="n">
         <v>79946</v>
@@ -11495,10 +11527,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>421343</v>
+        <v>421246</v>
       </c>
       <c r="R98" t="n">
-        <v>6788400</v>
+        <v>6788416</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11530,7 +11562,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11540,7 +11572,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11566,13 +11598,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124056</t>
+          <t>https://artportalen.se/Sighting/129124058</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129124057</v>
+        <v>129124059</v>
       </c>
       <c r="B99" t="n">
         <v>79946</v>
@@ -11607,10 +11639,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>421312</v>
+        <v>421354</v>
       </c>
       <c r="R99" t="n">
-        <v>6788393</v>
+        <v>6788463</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11642,7 +11674,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11652,7 +11684,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11678,13 +11710,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124057</t>
+          <t>https://artportalen.se/Sighting/129124059</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129124058</v>
+        <v>129124060</v>
       </c>
       <c r="B100" t="n">
         <v>79946</v>
@@ -11719,10 +11751,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>421246</v>
+        <v>421338</v>
       </c>
       <c r="R100" t="n">
-        <v>6788416</v>
+        <v>6788476</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11754,7 +11786,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11764,7 +11796,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11790,13 +11822,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124058</t>
+          <t>https://artportalen.se/Sighting/129124060</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129124059</v>
+        <v>129124061</v>
       </c>
       <c r="B101" t="n">
         <v>79946</v>
@@ -11831,10 +11863,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>421354</v>
+        <v>421238</v>
       </c>
       <c r="R101" t="n">
-        <v>6788463</v>
+        <v>6788555</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11866,7 +11898,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11876,7 +11908,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11902,13 +11934,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124059</t>
+          <t>https://artportalen.se/Sighting/129124061</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129124060</v>
+        <v>129124062</v>
       </c>
       <c r="B102" t="n">
         <v>79946</v>
@@ -11943,10 +11975,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>421338</v>
+        <v>421395</v>
       </c>
       <c r="R102" t="n">
-        <v>6788476</v>
+        <v>6788610</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11978,7 +12010,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11988,7 +12020,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12014,13 +12046,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124060</t>
+          <t>https://artportalen.se/Sighting/129124062</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129124061</v>
+        <v>129124063</v>
       </c>
       <c r="B103" t="n">
         <v>79946</v>
@@ -12055,10 +12087,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>421238</v>
+        <v>421442</v>
       </c>
       <c r="R103" t="n">
-        <v>6788555</v>
+        <v>6788613</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12090,7 +12122,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12100,7 +12132,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12126,13 +12158,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124061</t>
+          <t>https://artportalen.se/Sighting/129124063</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129124062</v>
+        <v>129124064</v>
       </c>
       <c r="B104" t="n">
         <v>79946</v>
@@ -12167,10 +12199,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>421395</v>
+        <v>421501</v>
       </c>
       <c r="R104" t="n">
-        <v>6788610</v>
+        <v>6788671</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12202,7 +12234,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12212,7 +12244,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12238,13 +12270,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124062</t>
+          <t>https://artportalen.se/Sighting/129124064</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129124063</v>
+        <v>129124065</v>
       </c>
       <c r="B105" t="n">
         <v>79946</v>
@@ -12279,10 +12311,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>421442</v>
+        <v>421530</v>
       </c>
       <c r="R105" t="n">
-        <v>6788613</v>
+        <v>6788679</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12314,7 +12346,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12324,7 +12356,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12350,13 +12382,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124063</t>
+          <t>https://artportalen.se/Sighting/129124065</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129124064</v>
+        <v>129124066</v>
       </c>
       <c r="B106" t="n">
         <v>79946</v>
@@ -12391,10 +12423,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>421501</v>
+        <v>421685</v>
       </c>
       <c r="R106" t="n">
-        <v>6788671</v>
+        <v>6788462</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12426,7 +12458,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12436,7 +12468,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12462,13 +12494,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124064</t>
+          <t>https://artportalen.se/Sighting/129124066</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129124065</v>
+        <v>129124067</v>
       </c>
       <c r="B107" t="n">
         <v>79946</v>
@@ -12503,10 +12535,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>421530</v>
+        <v>421751</v>
       </c>
       <c r="R107" t="n">
-        <v>6788679</v>
+        <v>6788483</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12538,7 +12570,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12548,7 +12580,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12574,7 +12606,7 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124065</t>
+          <t>https://artportalen.se/Sighting/129124067</t>
         </is>
       </c>
     </row>
@@ -14071,54 +14103,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>88280081</v>
+        <v>129093117</v>
       </c>
       <c r="B121" t="n">
-        <v>12703</v>
+        <v>8455</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>105850</v>
+        <v>106545</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Corticeus longulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1827)</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>sållning</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Hädbodarna, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>421414</v>
+        <v>421391</v>
       </c>
       <c r="R121" t="n">
-        <v>6788091</v>
+        <v>6788314</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14145,17 +14168,22 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ett dött ex (torrt fragment) utanpå bark. Övriga arter: timmerman (kläckhål), barrträdlöpare och allmän barkplattbagge (larver), Phloenomus, troligen lapponica, Phloeopora testacea, Placusa, troligen depressa (många ex)</t>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14166,47 +14194,28 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>Gles tallskog på svag sydvästsluttning, delvis försumpad</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Nydöd tall 37 cm, gröna, gula, bruna och röda barr, med båda arter märgborrar</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars, Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr">
-        <is>
-          <t>Insekter på tallved i Dalarna 2020 - 2021</t>
-        </is>
-      </c>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88280081</t>
+          <t>https://artportalen.se/Sighting/129093117</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>88280082</v>
+        <v>129093853</v>
       </c>
       <c r="B122" t="n">
         <v>8455</v>
@@ -14235,21 +14244,16 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Hädbodarna, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>421414</v>
+        <v>421371</v>
       </c>
       <c r="R122" t="n">
-        <v>6788091</v>
+        <v>6788472</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14276,17 +14280,22 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Gnagspår och fragment, tillsammans med större märgborre. Den mindre föredrar tydligt sydsidan, här ned till 120 cm från rot</t>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14297,42 +14306,28 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>Gles tallskog på svag sydvästsluttning, delvis försumpad</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Nydöd tall 37 cm, gröna, gula, bruna och röda barr</t>
-        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars, Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY122" t="inlineStr">
-        <is>
-          <t>Insekter på tallved i Dalarna 2020 - 2021</t>
-        </is>
-      </c>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88280082</t>
+          <t>https://artportalen.se/Sighting/129093853</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129093117</v>
+        <v>129093945</v>
       </c>
       <c r="B123" t="n">
         <v>8455</v>
@@ -14367,10 +14362,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>421391</v>
+        <v>421399</v>
       </c>
       <c r="R123" t="n">
-        <v>6788314</v>
+        <v>6788487</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14438,13 +14433,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093117</t>
+          <t>https://artportalen.se/Sighting/129093945</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129093853</v>
+        <v>129094196</v>
       </c>
       <c r="B124" t="n">
         <v>8455</v>
@@ -14479,10 +14474,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>421371</v>
+        <v>421526</v>
       </c>
       <c r="R124" t="n">
-        <v>6788472</v>
+        <v>6788587</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14550,13 +14545,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093853</t>
+          <t>https://artportalen.se/Sighting/129094196</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129093945</v>
+        <v>129094249</v>
       </c>
       <c r="B125" t="n">
         <v>8455</v>
@@ -14591,10 +14586,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>421399</v>
+        <v>421564</v>
       </c>
       <c r="R125" t="n">
-        <v>6788487</v>
+        <v>6788544</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14662,13 +14657,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093945</t>
+          <t>https://artportalen.se/Sighting/129094249</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129094196</v>
+        <v>129124106</v>
       </c>
       <c r="B126" t="n">
         <v>8455</v>
@@ -14697,16 +14692,21 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>421526</v>
+        <v>421574</v>
       </c>
       <c r="R126" t="n">
-        <v>6788587</v>
+        <v>6788374</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14763,24 +14763,24 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094196</t>
+          <t>https://artportalen.se/Sighting/129124106</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129094249</v>
+        <v>129124107</v>
       </c>
       <c r="B127" t="n">
         <v>8455</v>
@@ -14809,16 +14809,21 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>421564</v>
+        <v>421451</v>
       </c>
       <c r="R127" t="n">
-        <v>6788544</v>
+        <v>6788307</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14850,7 +14855,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14860,7 +14865,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14875,24 +14880,24 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094249</t>
+          <t>https://artportalen.se/Sighting/129124107</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129124106</v>
+        <v>129124108</v>
       </c>
       <c r="B128" t="n">
         <v>8455</v>
@@ -14923,7 +14928,7 @@
       <c r="I128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -14932,10 +14937,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>421574</v>
+        <v>421362</v>
       </c>
       <c r="R128" t="n">
-        <v>6788374</v>
+        <v>6788387</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14967,7 +14972,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14977,7 +14982,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15003,13 +15008,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124106</t>
+          <t>https://artportalen.se/Sighting/129124108</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129124107</v>
+        <v>129124109</v>
       </c>
       <c r="B129" t="n">
         <v>8455</v>
@@ -15049,10 +15054,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>421451</v>
+        <v>421325</v>
       </c>
       <c r="R129" t="n">
-        <v>6788307</v>
+        <v>6788393</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15084,7 +15089,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15094,7 +15099,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15120,13 +15125,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124107</t>
+          <t>https://artportalen.se/Sighting/129124109</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129124108</v>
+        <v>129124110</v>
       </c>
       <c r="B130" t="n">
         <v>8455</v>
@@ -15166,10 +15171,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>421362</v>
+        <v>421271</v>
       </c>
       <c r="R130" t="n">
-        <v>6788387</v>
+        <v>6788430</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15201,7 +15206,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15211,7 +15216,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15237,13 +15242,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124108</t>
+          <t>https://artportalen.se/Sighting/129124110</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129124109</v>
+        <v>129124111</v>
       </c>
       <c r="B131" t="n">
         <v>8455</v>
@@ -15283,10 +15288,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>421325</v>
+        <v>421315</v>
       </c>
       <c r="R131" t="n">
-        <v>6788393</v>
+        <v>6788532</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15318,7 +15323,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15328,7 +15333,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15354,13 +15359,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124109</t>
+          <t>https://artportalen.se/Sighting/129124111</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129124110</v>
+        <v>129124112</v>
       </c>
       <c r="B132" t="n">
         <v>8455</v>
@@ -15400,10 +15405,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>421271</v>
+        <v>421293</v>
       </c>
       <c r="R132" t="n">
-        <v>6788430</v>
+        <v>6788551</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15435,7 +15440,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15445,7 +15450,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15471,13 +15476,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124110</t>
+          <t>https://artportalen.se/Sighting/129124112</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129124111</v>
+        <v>129124114</v>
       </c>
       <c r="B133" t="n">
         <v>8455</v>
@@ -15517,10 +15522,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>421315</v>
+        <v>421399</v>
       </c>
       <c r="R133" t="n">
-        <v>6788532</v>
+        <v>6788567</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15552,7 +15557,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15562,7 +15567,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15588,13 +15593,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124111</t>
+          <t>https://artportalen.se/Sighting/129124114</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129124112</v>
+        <v>129124115</v>
       </c>
       <c r="B134" t="n">
         <v>8455</v>
@@ -15634,10 +15639,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>421293</v>
+        <v>421608</v>
       </c>
       <c r="R134" t="n">
-        <v>6788551</v>
+        <v>6788661</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15669,7 +15674,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15679,7 +15684,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15705,13 +15710,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124112</t>
+          <t>https://artportalen.se/Sighting/129124115</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129124114</v>
+        <v>129124116</v>
       </c>
       <c r="B135" t="n">
         <v>8455</v>
@@ -15751,10 +15756,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>421399</v>
+        <v>421615</v>
       </c>
       <c r="R135" t="n">
-        <v>6788567</v>
+        <v>6788580</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15786,7 +15791,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15796,7 +15801,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15822,13 +15827,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124114</t>
+          <t>https://artportalen.se/Sighting/129124116</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129124115</v>
+        <v>129124117</v>
       </c>
       <c r="B136" t="n">
         <v>8455</v>
@@ -15868,10 +15873,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>421608</v>
+        <v>421611</v>
       </c>
       <c r="R136" t="n">
-        <v>6788661</v>
+        <v>6788482</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15903,7 +15908,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15913,7 +15918,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15939,13 +15944,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124115</t>
+          <t>https://artportalen.se/Sighting/129124117</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129124116</v>
+        <v>129124118</v>
       </c>
       <c r="B137" t="n">
         <v>8455</v>
@@ -15985,10 +15990,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>421615</v>
+        <v>421732</v>
       </c>
       <c r="R137" t="n">
-        <v>6788580</v>
+        <v>6788486</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16020,7 +16025,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16030,7 +16035,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16056,13 +16061,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124116</t>
+          <t>https://artportalen.se/Sighting/129124118</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129124117</v>
+        <v>129124119</v>
       </c>
       <c r="B138" t="n">
         <v>8455</v>
@@ -16102,10 +16107,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>421611</v>
+        <v>421653</v>
       </c>
       <c r="R138" t="n">
-        <v>6788482</v>
+        <v>6788387</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16137,7 +16142,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16147,7 +16152,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16173,13 +16178,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124117</t>
+          <t>https://artportalen.se/Sighting/129124119</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129124119</v>
+        <v>129124120</v>
       </c>
       <c r="B139" t="n">
         <v>8455</v>
@@ -16219,10 +16224,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>421653</v>
+        <v>421520</v>
       </c>
       <c r="R139" t="n">
-        <v>6788387</v>
+        <v>6788366</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16254,7 +16259,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16264,7 +16269,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16290,13 +16295,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124119</t>
+          <t>https://artportalen.se/Sighting/129124120</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129124120</v>
+        <v>129124121</v>
       </c>
       <c r="B140" t="n">
         <v>8455</v>
@@ -16336,10 +16341,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>421520</v>
+        <v>421524</v>
       </c>
       <c r="R140" t="n">
-        <v>6788366</v>
+        <v>6788399</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16371,7 +16376,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16381,7 +16386,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16407,13 +16412,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124120</t>
+          <t>https://artportalen.se/Sighting/129124121</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129124121</v>
+        <v>129124122</v>
       </c>
       <c r="B141" t="n">
         <v>8455</v>
@@ -16453,10 +16458,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>421524</v>
+        <v>421477</v>
       </c>
       <c r="R141" t="n">
-        <v>6788399</v>
+        <v>6788422</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16488,7 +16493,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16498,7 +16503,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16524,13 +16529,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124121</t>
+          <t>https://artportalen.se/Sighting/129124122</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129124122</v>
+        <v>129124123</v>
       </c>
       <c r="B142" t="n">
         <v>8455</v>
@@ -16570,10 +16575,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>421477</v>
+        <v>421446</v>
       </c>
       <c r="R142" t="n">
-        <v>6788422</v>
+        <v>6788421</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16605,7 +16610,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16615,7 +16620,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16641,13 +16646,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124122</t>
+          <t>https://artportalen.se/Sighting/129124123</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129124123</v>
+        <v>129124124</v>
       </c>
       <c r="B143" t="n">
         <v>8455</v>
@@ -16687,10 +16692,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>421446</v>
+        <v>421440</v>
       </c>
       <c r="R143" t="n">
-        <v>6788421</v>
+        <v>6788409</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16722,7 +16727,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16732,7 +16737,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16758,13 +16763,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124123</t>
+          <t>https://artportalen.se/Sighting/129124124</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129124124</v>
+        <v>129124125</v>
       </c>
       <c r="B144" t="n">
         <v>8455</v>
@@ -16804,10 +16809,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>421440</v>
+        <v>421369</v>
       </c>
       <c r="R144" t="n">
-        <v>6788409</v>
+        <v>6788395</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16839,7 +16844,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16849,7 +16854,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16875,13 +16880,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124124</t>
+          <t>https://artportalen.se/Sighting/129124125</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129124125</v>
+        <v>129124126</v>
       </c>
       <c r="B145" t="n">
         <v>8455</v>
@@ -16921,10 +16926,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>421369</v>
+        <v>421654</v>
       </c>
       <c r="R145" t="n">
-        <v>6788395</v>
+        <v>6787690</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16956,7 +16961,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16966,7 +16971,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16992,13 +16997,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124125</t>
+          <t>https://artportalen.se/Sighting/129124126</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129124126</v>
+        <v>129124127</v>
       </c>
       <c r="B146" t="n">
         <v>8455</v>
@@ -17038,10 +17043,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>421654</v>
+        <v>421630</v>
       </c>
       <c r="R146" t="n">
-        <v>6787690</v>
+        <v>6787815</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17073,7 +17078,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17083,7 +17088,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17109,16 +17114,16 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124126</t>
+          <t>https://artportalen.se/Sighting/129124127</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129124127</v>
+        <v>137403526</v>
       </c>
       <c r="B147" t="n">
-        <v>8455</v>
+        <v>8470</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17144,24 +17149,20 @@
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>421630</v>
+        <v>421205</v>
       </c>
       <c r="R147" t="n">
-        <v>6787815</v>
+        <v>6788671</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -17185,22 +17186,22 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17215,66 +17216,65 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Eva Löfqvist, Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124127</t>
+          <t>https://artportalen.se/Sighting/137403526</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>137403526</v>
+        <v>129095730</v>
       </c>
       <c r="B148" t="n">
-        <v>8470</v>
+        <v>79085</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>421205</v>
+        <v>421655</v>
       </c>
       <c r="R148" t="n">
-        <v>6788671</v>
+        <v>6787687</v>
       </c>
       <c r="S148" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17298,22 +17298,22 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17328,24 +17328,24 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137403526</t>
+          <t>https://artportalen.se/Sighting/129095730</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129095730</v>
+        <v>129124103</v>
       </c>
       <c r="B149" t="n">
         <v>79085</v>
@@ -17376,14 +17376,14 @@
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>421655</v>
+        <v>421618</v>
       </c>
       <c r="R149" t="n">
-        <v>6787687</v>
+        <v>6787832</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17415,7 +17415,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17425,7 +17425,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17440,24 +17440,24 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095730</t>
+          <t>https://artportalen.se/Sighting/129124103</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129124103</v>
+        <v>129124128</v>
       </c>
       <c r="B150" t="n">
         <v>79085</v>
@@ -17492,10 +17492,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>421618</v>
+        <v>421391</v>
       </c>
       <c r="R150" t="n">
-        <v>6787832</v>
+        <v>6788209</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17563,13 +17563,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124103</t>
+          <t>https://artportalen.se/Sighting/129124128</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129124128</v>
+        <v>129124129</v>
       </c>
       <c r="B151" t="n">
         <v>79085</v>
@@ -17604,10 +17604,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>421391</v>
+        <v>421292</v>
       </c>
       <c r="R151" t="n">
-        <v>6788209</v>
+        <v>6788456</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17639,7 +17639,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17649,7 +17649,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17675,13 +17675,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124128</t>
+          <t>https://artportalen.se/Sighting/129124129</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129124129</v>
+        <v>129124130</v>
       </c>
       <c r="B152" t="n">
         <v>79085</v>
@@ -17716,10 +17716,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>421292</v>
+        <v>421354</v>
       </c>
       <c r="R152" t="n">
-        <v>6788456</v>
+        <v>6788463</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17751,7 +17751,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17761,7 +17761,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17787,13 +17787,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124129</t>
+          <t>https://artportalen.se/Sighting/129124130</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129124130</v>
+        <v>129124131</v>
       </c>
       <c r="B153" t="n">
         <v>79085</v>
@@ -17828,10 +17828,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>421354</v>
+        <v>421659</v>
       </c>
       <c r="R153" t="n">
-        <v>6788463</v>
+        <v>6787750</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17899,13 +17899,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124130</t>
+          <t>https://artportalen.se/Sighting/129124131</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129124131</v>
+        <v>129124132</v>
       </c>
       <c r="B154" t="n">
         <v>79085</v>
@@ -17940,10 +17940,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>421659</v>
+        <v>421649</v>
       </c>
       <c r="R154" t="n">
-        <v>6787750</v>
+        <v>6787778</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17975,7 +17975,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17985,7 +17985,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18011,13 +18011,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124131</t>
+          <t>https://artportalen.se/Sighting/129124132</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129124132</v>
+        <v>129124133</v>
       </c>
       <c r="B155" t="n">
         <v>79085</v>
@@ -18052,10 +18052,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>421649</v>
+        <v>421633</v>
       </c>
       <c r="R155" t="n">
-        <v>6787778</v>
+        <v>6787841</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18087,7 +18087,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18097,7 +18097,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18123,13 +18123,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124132</t>
+          <t>https://artportalen.se/Sighting/129124133</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129124133</v>
+        <v>129124134</v>
       </c>
       <c r="B156" t="n">
         <v>79085</v>
@@ -18164,10 +18164,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>421633</v>
+        <v>421616</v>
       </c>
       <c r="R156" t="n">
-        <v>6787841</v>
+        <v>6787882</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18209,7 +18209,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18235,13 +18235,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124133</t>
+          <t>https://artportalen.se/Sighting/129124134</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129124134</v>
+        <v>129124135</v>
       </c>
       <c r="B157" t="n">
         <v>79085</v>
@@ -18276,10 +18276,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>421616</v>
+        <v>421594</v>
       </c>
       <c r="R157" t="n">
-        <v>6787882</v>
+        <v>6787870</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18311,7 +18311,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18321,7 +18321,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18347,13 +18347,13 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124134</t>
+          <t>https://artportalen.se/Sighting/129124135</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129124135</v>
+        <v>129124136</v>
       </c>
       <c r="B158" t="n">
         <v>79085</v>
@@ -18388,10 +18388,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>421594</v>
+        <v>421598</v>
       </c>
       <c r="R158" t="n">
-        <v>6787870</v>
+        <v>6787834</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18423,7 +18423,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18433,7 +18433,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18459,16 +18459,16 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124135</t>
+          <t>https://artportalen.se/Sighting/129124136</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129124136</v>
+        <v>129093598</v>
       </c>
       <c r="B159" t="n">
-        <v>79085</v>
+        <v>79917</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18476,34 +18476,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Blåfljot, Dlr</t>
+          <t>Häden, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>421598</v>
+        <v>421371</v>
       </c>
       <c r="R159" t="n">
-        <v>6787834</v>
+        <v>6788472</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18535,7 +18535,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18545,7 +18545,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18560,24 +18560,24 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124136</t>
+          <t>https://artportalen.se/Sighting/129093598</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129093598</v>
+        <v>129094076</v>
       </c>
       <c r="B160" t="n">
         <v>79917</v>
@@ -18612,10 +18612,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>421371</v>
+        <v>421379</v>
       </c>
       <c r="R160" t="n">
-        <v>6788472</v>
+        <v>6788540</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18683,13 +18683,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129093598</t>
+          <t>https://artportalen.se/Sighting/129094076</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129094076</v>
+        <v>129094542</v>
       </c>
       <c r="B161" t="n">
         <v>79917</v>
@@ -18724,10 +18724,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>421379</v>
+        <v>421564</v>
       </c>
       <c r="R161" t="n">
-        <v>6788540</v>
+        <v>6788544</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18795,13 +18795,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094076</t>
+          <t>https://artportalen.se/Sighting/129094542</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129094542</v>
+        <v>129094943</v>
       </c>
       <c r="B162" t="n">
         <v>79917</v>
@@ -18836,10 +18836,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>421564</v>
+        <v>421534</v>
       </c>
       <c r="R162" t="n">
-        <v>6788544</v>
+        <v>6788452</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18907,13 +18907,13 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094542</t>
+          <t>https://artportalen.se/Sighting/129094943</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129094943</v>
+        <v>129095743</v>
       </c>
       <c r="B163" t="n">
         <v>79917</v>
@@ -18948,10 +18948,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>421534</v>
+        <v>421655</v>
       </c>
       <c r="R163" t="n">
-        <v>6788452</v>
+        <v>6787687</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19019,13 +19019,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129094943</t>
+          <t>https://artportalen.se/Sighting/129095743</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129095743</v>
+        <v>129095886</v>
       </c>
       <c r="B164" t="n">
         <v>79917</v>
@@ -19060,10 +19060,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>421655</v>
+        <v>421623</v>
       </c>
       <c r="R164" t="n">
-        <v>6787687</v>
+        <v>6787731</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19131,13 +19131,13 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095743</t>
+          <t>https://artportalen.se/Sighting/129095886</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129095886</v>
+        <v>129095952</v>
       </c>
       <c r="B165" t="n">
         <v>79917</v>
@@ -19172,10 +19172,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>421623</v>
+        <v>421617</v>
       </c>
       <c r="R165" t="n">
-        <v>6787731</v>
+        <v>6787742</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19243,13 +19243,13 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095886</t>
+          <t>https://artportalen.se/Sighting/129095952</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129095952</v>
+        <v>129124074</v>
       </c>
       <c r="B166" t="n">
         <v>79917</v>
@@ -19280,14 +19280,14 @@
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Häden, Dlr</t>
+          <t>Blåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>421617</v>
+        <v>421236</v>
       </c>
       <c r="R166" t="n">
-        <v>6787742</v>
+        <v>6788559</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19319,7 +19319,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19329,7 +19329,12 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>På stubbe med 6 brandljud</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19344,24 +19349,24 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129095952</t>
+          <t>https://artportalen.se/Sighting/129124074</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129124074</v>
+        <v>129124075</v>
       </c>
       <c r="B167" t="n">
         <v>79917</v>
@@ -19396,10 +19401,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>421236</v>
+        <v>421449</v>
       </c>
       <c r="R167" t="n">
-        <v>6788559</v>
+        <v>6788278</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19431,7 +19436,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19441,12 +19446,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>På stubbe med 6 brandljud</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19472,13 +19472,13 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124074</t>
+          <t>https://artportalen.se/Sighting/129124075</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129124075</v>
+        <v>129124076</v>
       </c>
       <c r="B168" t="n">
         <v>79917</v>
@@ -19513,10 +19513,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>421449</v>
+        <v>421240</v>
       </c>
       <c r="R168" t="n">
-        <v>6788278</v>
+        <v>6788558</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19548,7 +19548,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -19558,7 +19558,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19584,13 +19584,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124075</t>
+          <t>https://artportalen.se/Sighting/129124076</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129124076</v>
+        <v>129124077</v>
       </c>
       <c r="B169" t="n">
         <v>79917</v>
@@ -19625,10 +19625,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>421240</v>
+        <v>421633</v>
       </c>
       <c r="R169" t="n">
-        <v>6788558</v>
+        <v>6788617</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19660,7 +19660,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -19670,7 +19670,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19696,13 +19696,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124076</t>
+          <t>https://artportalen.se/Sighting/129124077</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129124077</v>
+        <v>129124078</v>
       </c>
       <c r="B170" t="n">
         <v>79917</v>
@@ -19737,10 +19737,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>421633</v>
+        <v>421640</v>
       </c>
       <c r="R170" t="n">
-        <v>6788617</v>
+        <v>6788394</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19772,7 +19772,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19808,13 +19808,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124077</t>
+          <t>https://artportalen.se/Sighting/129124078</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129124078</v>
+        <v>129124079</v>
       </c>
       <c r="B171" t="n">
         <v>79917</v>
@@ -19849,10 +19849,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>421640</v>
+        <v>421652</v>
       </c>
       <c r="R171" t="n">
-        <v>6788394</v>
+        <v>6787685</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19920,13 +19920,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124078</t>
+          <t>https://artportalen.se/Sighting/129124079</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129124079</v>
+        <v>129124080</v>
       </c>
       <c r="B172" t="n">
         <v>79917</v>
@@ -19961,10 +19961,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>421652</v>
+        <v>421633</v>
       </c>
       <c r="R172" t="n">
-        <v>6787685</v>
+        <v>6787841</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -20006,7 +20006,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20032,13 +20032,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124079</t>
+          <t>https://artportalen.se/Sighting/129124080</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129124080</v>
+        <v>129124081</v>
       </c>
       <c r="B173" t="n">
         <v>79917</v>
@@ -20073,10 +20073,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>421633</v>
+        <v>421592</v>
       </c>
       <c r="R173" t="n">
-        <v>6787841</v>
+        <v>6787842</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -20118,7 +20118,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20144,13 +20144,13 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124080</t>
+          <t>https://artportalen.se/Sighting/129124081</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129124081</v>
+        <v>129124082</v>
       </c>
       <c r="B174" t="n">
         <v>79917</v>
@@ -20185,10 +20185,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>421592</v>
+        <v>421601</v>
       </c>
       <c r="R174" t="n">
-        <v>6787842</v>
+        <v>6787830</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20220,7 +20220,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -20230,7 +20230,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20256,13 +20256,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124081</t>
+          <t>https://artportalen.se/Sighting/129124082</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129124082</v>
+        <v>129124083</v>
       </c>
       <c r="B175" t="n">
         <v>79917</v>
@@ -20297,10 +20297,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>421601</v>
+        <v>421598</v>
       </c>
       <c r="R175" t="n">
-        <v>6787830</v>
+        <v>6787829</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20368,13 +20368,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124082</t>
+          <t>https://artportalen.se/Sighting/129124083</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129124083</v>
+        <v>129124084</v>
       </c>
       <c r="B176" t="n">
         <v>79917</v>
@@ -20409,10 +20409,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>421598</v>
+        <v>421591</v>
       </c>
       <c r="R176" t="n">
-        <v>6787829</v>
+        <v>6787819</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20444,7 +20444,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20480,13 +20480,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124083</t>
+          <t>https://artportalen.se/Sighting/129124084</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129124084</v>
+        <v>129124085</v>
       </c>
       <c r="B177" t="n">
         <v>79917</v>
@@ -20521,10 +20521,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>421591</v>
+        <v>421622</v>
       </c>
       <c r="R177" t="n">
-        <v>6787819</v>
+        <v>6787726</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -20566,7 +20566,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20592,16 +20592,16 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124084</t>
+          <t>https://artportalen.se/Sighting/129124085</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129124085</v>
+        <v>129124091</v>
       </c>
       <c r="B178" t="n">
-        <v>79917</v>
+        <v>79350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20609,21 +20609,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>229821</v>
+        <v>260591</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -20633,10 +20633,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>421622</v>
+        <v>421255</v>
       </c>
       <c r="R178" t="n">
-        <v>6787726</v>
+        <v>6788442</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20668,7 +20668,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -20678,7 +20678,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20704,13 +20704,13 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124085</t>
+          <t>https://artportalen.se/Sighting/129124091</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129124091</v>
+        <v>129124092</v>
       </c>
       <c r="B179" t="n">
         <v>79350</v>
@@ -20745,10 +20745,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>421255</v>
+        <v>421696</v>
       </c>
       <c r="R179" t="n">
-        <v>6788442</v>
+        <v>6788469</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20780,7 +20780,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -20790,7 +20790,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20816,7 +20816,7 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129124091</t>
+          <t>https://artportalen.se/Sighting/129124092</t>
         </is>
       </c>
     </row>
@@ -20825,7 +20825,7 @@
         <v>137209425</v>
       </c>
       <c r="B180" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>137403524</v>
       </c>
       <c r="B181" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
